--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E592A495-118B-4107-B2E3-9102D5CE76BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5098AFC6-35DC-4CC0-B8E4-FB8B1EDD8C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="38">
   <si>
     <t>ERRO</t>
   </si>
@@ -62,112 +62,97 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>eliana.pedroso@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12875744700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+    <t>raquel.sech@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13338667600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
   </si>
   <si>
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>lilian.sudati@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13064449300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>ana.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13334392800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>jessika.pazin@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13310983800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>fernando.duque@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13342685900000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>bruno.rosa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13287094100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>caroline.wojciechowski@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13337711100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>andre.gouvea@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13337428400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>andriele.pala@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13346968300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>everton.silva1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13342325400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>leticia.pitkowski@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13342817900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>raullison.castro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13334482100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>leandro.susanj@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13002142400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13343027800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>lais.xavier@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13332963600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+    <t>edirilsa.bastos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13343004700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>erica.cassandre@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13334170900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>adriana.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13333544000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13341301400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>marina.melo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13341334000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>marco.schiabel@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13341458900000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>karen.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13344682000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>leonardo.castro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13340007600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>maria.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13348246300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>rafael.leite@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13295347100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>rosemeire.faria@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13097696500000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>ivone.jesus@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13323269900000 Nota 167 - Retorno Cobrança</t>
   </si>
   <si>
     <t>cristiane.lozano@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13287136100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>marli.rocha@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13342817900000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>laerte.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13282608600000 Nota 167 - Retorno Cobrança</t>
+    <t>Retorno de GO referência-13342307100000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>karina.vieira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13126600900000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13174103300000 Nota 167 - Retorno Cobrança</t>
   </si>
 </sst>
 </file>
@@ -667,10 +652,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>16</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>9</v>
@@ -682,10 +667,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>18</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>19</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>9</v>
@@ -697,10 +682,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>21</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>9</v>
@@ -712,10 +697,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>23</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>9</v>
@@ -727,10 +712,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>24</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>25</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>9</v>
@@ -742,10 +727,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>26</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>27</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>9</v>
@@ -757,10 +742,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>29</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>9</v>
@@ -772,10 +757,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>9</v>
@@ -787,10 +772,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>32</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>33</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>9</v>
@@ -802,7 +787,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>34</v>
@@ -832,11 +817,11 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>38</v>
-      </c>
       <c r="C17" s="10" t="s">
         <v>9</v>
       </c>
@@ -846,33 +831,13 @@
       <c r="F17" s="3"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="C18" s="10"/>
+      <c r="D18" s="5"/>
       <c r="F18" s="6"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="C19" s="10"/>
+      <c r="D19" s="5"/>
       <c r="F19" s="3"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">

--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5098AFC6-35DC-4CC0-B8E4-FB8B1EDD8C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{064BF896-D2E6-423F-81C3-172FA7664655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="54">
   <si>
     <t>ERRO</t>
   </si>
@@ -62,97 +62,145 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>raquel.sech@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13338667600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+    <t>crislaine.trindade@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13320417900000 Nota 7022 - Help Desk</t>
   </si>
   <si>
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>edirilsa.bastos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13343004700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>erica.cassandre@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13334170900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>adriana.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13333544000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13341301400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>marina.melo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13341334000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>marco.schiabel@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13341458900000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>karen.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13344682000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>leonardo.castro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13340007600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>maria.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13348246300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>rafael.leite@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13295347100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>rosemeire.faria@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13097696500000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>ivone.jesus@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13323269900000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>cristiane.lozano@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13342307100000 Nota 472 - Reentrada OK Produto</t>
+    <t>diego.vasconcelos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13340203800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>kaue.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13331713100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>claudia.ribeiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13332322600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>aguinaldo.junior@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13337261200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>flavio.cesar@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13338118100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>vanessa.campos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13350322600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>yuri.santos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12882047400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>lidiane.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13350448300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>monica.prates@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13277515200000 Nota 7022 - Help Desk</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13338956100000 Nota 7022 - Help Desk</t>
+  </si>
+  <si>
+    <t>lucas.godinho@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13328300700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>ana.cunha@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13346456700000 Nota 7022 - Help Desk</t>
+  </si>
+  <si>
+    <t>rodrigo.amorim@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13304442700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>andrea.farias1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13092926100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>fabiola.caixeta@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13339953400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>marli.rocha@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13006148900000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>ana.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13180537600000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>anderson.menezes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-10578739700000 Nota 742 - Prêmio</t>
+  </si>
+  <si>
+    <t>vanessa.amaral@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13339686300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
   </si>
   <si>
     <t>karina.vieira@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13126600900000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13174103300000 Nota 167 - Retorno Cobrança</t>
+    <t>Retorno de GO referência-12448112600000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>renata.souza1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13117129100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>carlos.neves@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12504787400000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12680202700000 Nota 242 - Retorno Cobrança</t>
   </si>
 </sst>
 </file>
@@ -652,10 +700,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>9</v>
@@ -667,10 +715,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>9</v>
@@ -682,10 +730,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>9</v>
@@ -697,10 +745,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>9</v>
@@ -712,10 +760,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>9</v>
@@ -727,10 +775,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>9</v>
@@ -742,7 +790,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>28</v>
@@ -817,10 +865,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>9</v>
@@ -831,38 +879,121 @@
       <c r="F17" s="3"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C18" s="10"/>
-      <c r="D18" s="5"/>
+      <c r="A18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="F18" s="6"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C19" s="10"/>
-      <c r="D19" s="5"/>
+      <c r="A19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="F19" s="3"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C20" s="10"/>
-      <c r="D20" s="5"/>
+      <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="F20" s="6"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C21" s="10"/>
-      <c r="D21" s="5"/>
+      <c r="A21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="F21" s="3"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C22" s="10"/>
-      <c r="D22" s="5"/>
+      <c r="A22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="F22" s="6"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D23" s="5"/>
+      <c r="A23" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D24" s="5"/>
+      <c r="A24" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D25" s="5"/>
+      <c r="A25" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D26" s="5"/>

--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB0297F-82B0-42D7-B889-DD698EC3362E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E0B09C6-01E9-44FF-B259-93C65DF850FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="36">
   <si>
     <t>ERRO</t>
   </si>
@@ -62,49 +62,91 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>claudia.ribeiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13337975000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+    <t>thamires.nascimento@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13045804700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
   </si>
   <si>
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>mariana.dolence@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11168729947 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>claudia.pires@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13353815100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>daniel.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13345024400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>jamaica.saldanha@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-10635691000153 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13297072200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>karina.vieira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12448063500000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12762122900000 Nota 167 - Retorno Cobrança</t>
+    <t>kaue.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13353768700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>juliano.guimaraes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13274889100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13334526500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>fabio.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13320327600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>william.rosa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13347410000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>renata.magalhaes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13344532500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>claudia.assuncao@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13228954900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>diogo.junior@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13346518100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>rafael.junior@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13339828200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>raullison.castro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13344966400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>carla.nascimento@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12881187600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>anderson.menezes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13270678600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>carlos.neves@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11895004900000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12712428600000 Nota 242 - Retorno Cobrança</t>
   </si>
 </sst>
 </file>
@@ -589,10 +631,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>14</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>15</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>9</v>
@@ -604,10 +646,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>16</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>9</v>
@@ -619,7 +661,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>18</v>
@@ -649,10 +691,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>9</v>
@@ -663,38 +705,108 @@
       <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C10" s="10"/>
-      <c r="D10" s="5"/>
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C11" s="10"/>
-      <c r="D11" s="5"/>
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="F11" s="3"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C12" s="10"/>
-      <c r="D12" s="5"/>
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="F12" s="6"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C13" s="10"/>
-      <c r="D13" s="5"/>
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C14" s="10"/>
-      <c r="D14" s="5"/>
+      <c r="A14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="F14" s="6"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C15" s="10"/>
-      <c r="D15" s="5"/>
+      <c r="A15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="F15" s="3"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C16" s="10"/>
-      <c r="D16" s="5"/>
+      <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="F16" s="6"/>
     </row>
     <row r="17" spans="3:6" x14ac:dyDescent="0.25">

--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2A9C1DC-D3C1-4062-A6E2-A15B08330459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C38AEDC9-A8B3-47E4-90A6-27DED1016FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="40">
   <si>
     <t>ERRO</t>
   </si>
@@ -62,97 +62,103 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>ana.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13334392800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+    <t>daniel.iarrocheski@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13112768200000 Nota 7022 - Help Desk</t>
   </si>
   <si>
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
+    <t>eliana.pedroso@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13344403400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>marilia.martins@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13352120800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>kaue.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13088656800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
     <t>juliano.guimaraes@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13274889100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+    <t>Retorno de GO referência-13357441000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
   </si>
   <si>
     <t>aguinaldo.junior@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13334047900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>eugenio.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13347084000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>flavio.cesar@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13018960700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>patricia.farias@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13349871700000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>gisele.cardoso1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13347996900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>claudia.pires@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13279536900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>bruna.teixeira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13339621400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>wagner.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13323671700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>fernando.sousa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13348295700000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>ana.rodrigues@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13334940000000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>rosana.pessoa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13326090600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>carla.catalani@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-53593934000140 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>dayane.germano@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13035572500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+    <t>Retorno de GO referência-13341773200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>daniela.leal@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13094486100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>bruno.rosa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13232444100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>carla.ventura@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13353101000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>luciana.belisario@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13267436400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>andreza.libanore@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13131074800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>saulo.santiago@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13353172900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>gustavo.correa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13329829600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>laiane.martins@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13354477900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>rafael.junior@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13334608900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>eudmila.tassara@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13296638500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
   </si>
 </sst>
 </file>
@@ -815,64 +821,74 @@
       </c>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C17" s="10"/>
-      <c r="D17" s="5"/>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="F17" s="3"/>
     </row>
-    <row r="18" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C18" s="10"/>
       <c r="D18" s="5"/>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C19" s="10"/>
       <c r="D19" s="5"/>
       <c r="F19" s="3"/>
     </row>
-    <row r="20" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C20" s="10"/>
       <c r="D20" s="5"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C21" s="10"/>
       <c r="D21" s="5"/>
       <c r="F21" s="3"/>
     </row>
-    <row r="22" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C22" s="10"/>
       <c r="D22" s="5"/>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D23" s="5"/>
     </row>
-    <row r="24" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D24" s="5"/>
     </row>
-    <row r="25" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D25" s="5"/>
     </row>
-    <row r="26" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D26" s="5"/>
     </row>
-    <row r="27" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D27" s="5"/>
     </row>
-    <row r="28" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D28" s="5"/>
     </row>
-    <row r="29" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D29" s="5"/>
     </row>
-    <row r="30" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D30" s="5"/>
     </row>
-    <row r="31" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D31" s="5"/>
     </row>
-    <row r="32" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D32" s="5"/>
     </row>
     <row r="33" spans="4:4" x14ac:dyDescent="0.25">

--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C38AEDC9-A8B3-47E4-90A6-27DED1016FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C3B5ECE-C5A4-4AEC-A46F-51200A8B9FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,103 +62,103 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>daniel.iarrocheski@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13112768200000 Nota 7022 - Help Desk</t>
+    <t>claudia.ribeiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13339660000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
   </si>
   <si>
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>eliana.pedroso@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13344403400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>marilia.martins@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13352120800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>kaue.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13088656800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>juliano.guimaraes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13357441000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+    <t>angela.carmo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13341672000000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
   </si>
   <si>
     <t>aguinaldo.junior@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13341773200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>daniela.leal@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13094486100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>bruno.rosa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13232444100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+    <t>Retorno de GO referência-13231820200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>jose.neves@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13210463900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>tatiany.macedo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13358686500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>gisele.cardoso1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13051466600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
   </si>
   <si>
     <t>carla.ventura@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13353101000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>luciana.belisario@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13267436400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>andreza.libanore@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13131074800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>saulo.santiago@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13353172900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>gustavo.correa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13329829600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>laiane.martins@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13354477900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>rafael.junior@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13334608900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+    <t>Retorno de GO referência-13236824300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>mayara.sampaio@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13356692400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>everton.silva1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13229523800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
   </si>
   <si>
     <t>eudmila.tassara@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13296638500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+    <t>Retorno de GO referência-13357985000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>lais.xavier@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13361998900000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>thays.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-32625625000135 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>eduardo.santos1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13356148900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>daniella.andrade@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13358830400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>micael.siqueira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12906769700000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>carlos.neves@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12950658500000 Nota 242 - Retorno Cobrança</t>
   </si>
 </sst>
 </file>

--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2241595E-E749-4F7F-B07E-8A0A39B602C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C489177-7FCD-43C5-9EC3-7CD15EAE21D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RetornoGo" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="53">
   <si>
     <t>ERRO</t>
   </si>
@@ -62,208 +62,142 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>denise.nogueira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-49906914000105 Nota 242 - Retorno Cobrança</t>
+    <t>deise.santos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13237379800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
   </si>
   <si>
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>raphael.callado@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13371638700000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>priscila.santana@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13107858000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13366832700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>diego.vasconcelos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13362491100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>william.bonifacio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13370650100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>filipe.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13362112000000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>matheus.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13362510500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>samuel.martins@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13348057000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+    <t>sonia.bortoleto@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13345450000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>claudia.gomes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13369182900000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>ana.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13370094400000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>erica.cassandre@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13371024400000 Nota 595 - ERRO PDF RETORNO</t>
   </si>
   <si>
     <t>bruno.rosa@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13362960100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>ana.sales@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13356198500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>kaue.medeiros@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13370107500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>juliana.diniz@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13361232700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>renata.magalhaes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13184445300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13340789900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>claudia.assuncao@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13353216400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>luiz.sanchetta@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13363019000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>rubiane.bendlin@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13362166000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>vitor.mattos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13361956500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13366273800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>andreia.cardias@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13350760000000 Nota 595 - ERRO PDF retonrio</t>
-  </si>
-  <si>
-    <t>everton.silva1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13368081900000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>cassia.souza@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13364103300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>raullison.castro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13072222100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13236664400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+    <t>Retorno de GO referência-13370989900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>gisele.cardoso1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13356436500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>carla.ventura@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13359309700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>andriele.pala@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13367790200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>nilcea.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13294866800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13295092800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>clarissa.cavalli@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13350226300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>rodrigo.deus@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13369598800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>andrea.duarte@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13366309600000 Nota 595 - ERRO PDF retorno</t>
   </si>
   <si>
     <t>gabriela.logrado@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13365440600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>aline.madeira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12913207800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>jheniffer.emiliano@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13351336600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>leandro.susanj@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13360921200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>luiz.junior1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13361033100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>leinny.amorim@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13371267800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>marli.rocha@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12913207800000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>cristiane.lozano@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13059660500000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13340789900000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13357004000000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13357480400000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>anderson.menezes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-48083919000112 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+    <t>Retorno de GO referência-13368957700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13369037700000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>cristiane.konrad@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13065518200000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>ana.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13086648000000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>rosemeire.faria@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13295950900000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13296929100000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>karla.cunha@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13268648100000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>janaina.cazelato@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13351725500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>micael.siqueira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12906769700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>karla.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-14517191000259 Nota 242 - Retorno Cobrança</t>
   </si>
 </sst>
 </file>
@@ -748,10 +682,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>9</v>
@@ -763,10 +697,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>9</v>
@@ -778,10 +712,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>9</v>
@@ -793,10 +727,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>9</v>
@@ -808,10 +742,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>9</v>
@@ -823,10 +757,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>9</v>
@@ -838,10 +772,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>9</v>
@@ -853,7 +787,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>28</v>
@@ -913,10 +847,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>9</v>
@@ -928,7 +862,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>37</v>
@@ -1059,215 +993,72 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>51</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D26" s="5"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>54</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C27" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D27" s="5"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>56</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D28" s="5"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>58</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D29" s="5"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>60</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D30" s="5"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>62</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C31" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D31" s="5"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>64</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C32" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>66</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C33" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>68</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C34" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>68</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C35" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>68</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C36" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>68</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>73</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C38" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D32" s="5"/>
+    </row>
+    <row r="33" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D33" s="5"/>
+    </row>
+    <row r="34" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D34" s="5"/>
+    </row>
+    <row r="35" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D35" s="5"/>
+    </row>
+    <row r="36" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D36" s="5"/>
+    </row>
+    <row r="37" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D37" s="5"/>
+    </row>
+    <row r="38" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D38" s="5"/>
+    </row>
+    <row r="39" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D39" s="5"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D40" s="5"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D41" s="5"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D42" s="5"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D43" s="5"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D44" s="5"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D45" s="5"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D46" s="5"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D47" s="5"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D48" s="5"/>
     </row>
   </sheetData>

--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C489177-7FCD-43C5-9EC3-7CD15EAE21D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4E23D75-D0B6-4E0C-8B67-B922F787D358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1170" yWindow="1170" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="44">
   <si>
     <t>ERRO</t>
   </si>
@@ -62,142 +62,115 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>deise.santos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13237379800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+    <t>jose.mergulhao@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-61573796000166 Nota 242 - Retorno Cobrança</t>
   </si>
   <si>
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>sonia.bortoleto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13345450000000 Nota 595 - ERRO PDF retorno</t>
+    <t>leandro.machado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13252168300000 Nota 595 - ERRO PDF retorno</t>
   </si>
   <si>
     <t>claudia.gomes@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13369182900000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>ana.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13370094400000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>erica.cassandre@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13371024400000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>bruno.rosa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13370989900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>gisele.cardoso1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13356436500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>carla.ventura@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13359309700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>andriele.pala@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13367790200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>nilcea.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13294866800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13295092800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>clarissa.cavalli@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13350226300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>rodrigo.deus@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13369598800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>andrea.duarte@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13366309600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>gabriela.logrado@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13368957700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13369037700000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>cristiane.konrad@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13065518200000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>ana.rodrigues@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13086648000000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>rosemeire.faria@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13295950900000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13296929100000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>karla.cunha@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13268648100000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>janaina.cazelato@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13351725500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>micael.siqueira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12906769700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>karla.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-14517191000259 Nota 242 - Retorno Cobrança</t>
+    <t>Retorno de GO referência-13368422800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>lilian.sudati@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13347917200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>kaue.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13088656800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>juliano.guimaraes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13371799700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>juliana.diniz@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13350623800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>elisangela.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13372005800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>caroline.wojciechowski@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13369742300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>danillo.boem@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13252974300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>renato.faillace@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12910065200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>adalberto.souza@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13365773900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>andrea.farias1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13371944700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>eudmila.tassara@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-41620856000147 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>enriete.saucedo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13356078000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>marli.rocha@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13357591700000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>thomaz.jesus@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13174103300000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>odair.tavares@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13371944100000 Nota 595 - ERRO PDF retorno</t>
   </si>
 </sst>
 </file>
@@ -787,10 +760,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>9</v>
@@ -802,10 +775,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>9</v>
@@ -817,10 +790,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>9</v>
@@ -832,10 +805,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>9</v>
@@ -847,10 +820,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>9</v>
@@ -862,10 +835,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>9</v>
@@ -877,10 +850,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>9</v>
@@ -892,10 +865,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>9</v>
@@ -906,91 +879,28 @@
       <c r="F19" s="3"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="C20" s="10"/>
+      <c r="D20" s="5"/>
       <c r="F20" s="6"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="C21" s="10"/>
+      <c r="D21" s="5"/>
       <c r="F21" s="3"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="C22" s="10"/>
+      <c r="D22" s="5"/>
       <c r="F22" s="6"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>47</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C23" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D23" s="5"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>49</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D24" s="5"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>51</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C25" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D25" s="5"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D26" s="5"/>

--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4E23D75-D0B6-4E0C-8B67-B922F787D358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{319E53A3-AE3F-4797-BCB2-6D1C3290F02E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RetornoGo" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="56">
   <si>
     <t>ERRO</t>
   </si>
@@ -62,115 +62,151 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>jose.mergulhao@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-61573796000166 Nota 242 - Retorno Cobrança</t>
+    <t>sonia.bortoleto@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13371839500000 Nota 595 - ERRO PDF retorno</t>
   </si>
   <si>
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>leandro.machado@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13252168300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>claudia.gomes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13368422800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>lilian.sudati@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13347917200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>kaue.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13088656800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>juliano.guimaraes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13371799700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>juliana.diniz@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13350623800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>elisangela.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13372005800000 Nota 595 - ERRO PDF retorno</t>
+    <t>mary.leme@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13076735600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>adriano.guerra@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-55415608000179 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>edirilsa.bastos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13002827400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>mariana.dolence@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-33037822880 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>fernando.duque@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13360325800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>tatiany.macedo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13117741100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13371087100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>juliana.assis@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13371877800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>andreia.brixner@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13358298400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
   </si>
   <si>
     <t>caroline.wojciechowski@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13369742300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>danillo.boem@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13252974300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+    <t>Retorno de GO referência-13371606600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13372304400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>saulo.santiago@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13155551900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>nilcea.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13365578400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13376906600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>rosilene.nogueira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13366881000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13372043900000 Nota 595 - ERRO PDF retorno</t>
   </si>
   <si>
     <t>renato.faillace@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12910065200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+    <t>Retorno de GO referência-13371803600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>sonia.nascimento@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13314789800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>gabriela.logrado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13008476900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>graziela.salvioni@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13336883000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13367613400000 Nota 595 - ERRO PDF retorno</t>
   </si>
   <si>
     <t>adalberto.souza@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13365773900000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>andrea.farias1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13371944700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>eudmila.tassara@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-41620856000147 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>enriete.saucedo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13356078000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>marli.rocha@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13357591700000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>thomaz.jesus@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13174103300000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>odair.tavares@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13371944100000 Nota 595 - ERRO PDF retorno</t>
+    <t>Retorno de GO referência-13263180100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>wagner.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13343797200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13362606500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>julianna.kirillov@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13356021600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>carlos.neves@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12657054900000 Nota 242 - Retorno Cobrança</t>
   </si>
 </sst>
 </file>
@@ -715,10 +751,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>23</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>9</v>
@@ -730,10 +766,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>24</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>25</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>9</v>
@@ -745,10 +781,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>26</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>27</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>9</v>
@@ -760,10 +796,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>29</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>9</v>
@@ -775,10 +811,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>9</v>
@@ -790,10 +826,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>9</v>
@@ -805,10 +841,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>9</v>
@@ -820,10 +856,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>9</v>
@@ -835,10 +871,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>9</v>
@@ -850,10 +886,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>9</v>
@@ -865,51 +901,147 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" s="3"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" s="6"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B21" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" s="3"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C20" s="10"/>
-      <c r="D20" s="5"/>
-      <c r="F20" s="6"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C21" s="10"/>
-      <c r="D21" s="5"/>
+      <c r="C21" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="F21" s="3"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C22" s="10"/>
-      <c r="D22" s="5"/>
+      <c r="A22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="F22" s="6"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D23" s="5"/>
+      <c r="A23" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D24" s="5"/>
+      <c r="A24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D25" s="5"/>
+      <c r="A25" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D26" s="5"/>
+      <c r="A26" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D27" s="5"/>
+      <c r="A27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D28" s="5"/>
+      <c r="A28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D29" s="5"/>

--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{496C8858-56A8-4128-A3A2-C13E5B218E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F7F86F-5106-4F44-9913-FBDE4653D3A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="24">
   <si>
     <t>ERRO</t>
   </si>
@@ -62,166 +62,55 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>daniel.iarrocheski@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13355241400000 Nota 595 - ERRO PDF reporno</t>
+    <t>Retorno de GO referência-13286908300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
   </si>
   <si>
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>rosangela.silva1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13388621800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>rodrigo.kuguyama@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13391793600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>bruno.rosa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13370989900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>daiane.soares@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13383168700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>priscila.santana@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13107858000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>andreia.brixner@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13373171300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>afonso.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13043506000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>luciana.belisario@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13281893400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>claudia.assuncao@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13155150400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>vitor.mattos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13366273800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>eduardo.marques@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13377613900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>dayane.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13359852300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>jonatas.lauretto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13374451700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>bruna.carneiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13301286900000 Nota 7022 - Help Desk</t>
-  </si>
-  <si>
-    <t>thays.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13389532900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>eduardo.santos1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13254667700000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>laila.steil@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13384605000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>marli.rocha@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13063204800000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>cristiane.lozano@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13373447200000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>janaina.cazelato@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-17209466000102 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>ana.carneiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-61574273000134 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>eliete.sousa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12894702900000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13316944800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>simone.souza2@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13387529500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>rose.lourenco@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13392737000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>stefani.saracho@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13070848000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+    <t>Retorno de GO referência-13381673400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13373437200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13382296800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13258440600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13325827400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13059902700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13204479700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13391654600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13314836000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13222323100000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13381673400000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13384586000000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12913326700000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13012186800000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12956121100000 Nota 167 - Retorno Cobrança</t>
   </si>
 </sst>
 </file>
@@ -667,9 +556,7 @@
       <c r="B2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>9</v>
-      </c>
+      <c r="C2" s="8"/>
       <c r="D2" s="5" t="s">
         <v>6</v>
       </c>
@@ -677,14 +564,12 @@
     </row>
     <row r="3" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>9</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C3" s="8"/>
       <c r="D3" s="5" t="s">
         <v>6</v>
       </c>
@@ -692,28 +577,24 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>9</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C4" s="8"/>
       <c r="D4" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>9</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C5" s="10"/>
       <c r="D5" s="5" t="s">
         <v>6</v>
       </c>
@@ -721,14 +602,12 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>9</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C6" s="10"/>
       <c r="D6" s="5" t="s">
         <v>6</v>
       </c>
@@ -736,14 +615,12 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>9</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C7" s="10"/>
       <c r="D7" s="5" t="s">
         <v>6</v>
       </c>
@@ -751,14 +628,12 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>9</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C8" s="10"/>
       <c r="D8" s="5" t="s">
         <v>6</v>
       </c>
@@ -766,14 +641,12 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>9</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C9" s="10"/>
       <c r="D9" s="5" t="s">
         <v>6</v>
       </c>
@@ -781,14 +654,12 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>9</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C10" s="10"/>
       <c r="D10" s="5" t="s">
         <v>6</v>
       </c>
@@ -796,14 +667,12 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>9</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C11" s="10"/>
       <c r="D11" s="5" t="s">
         <v>6</v>
       </c>
@@ -811,14 +680,12 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>9</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C12" s="10"/>
       <c r="D12" s="5" t="s">
         <v>6</v>
       </c>
@@ -826,14 +693,12 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>9</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C13" s="10"/>
       <c r="D13" s="5" t="s">
         <v>6</v>
       </c>
@@ -841,14 +706,12 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>9</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C14" s="10"/>
       <c r="D14" s="5" t="s">
         <v>6</v>
       </c>
@@ -856,14 +719,12 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>9</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C15" s="10"/>
       <c r="D15" s="5" t="s">
         <v>6</v>
       </c>
@@ -871,14 +732,12 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>9</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C16" s="10"/>
       <c r="D16" s="5" t="s">
         <v>6</v>
       </c>
@@ -886,177 +745,59 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>9</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C17" s="10"/>
       <c r="D17" s="5" t="s">
         <v>6</v>
       </c>
       <c r="F17" s="3"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="C18" s="10"/>
+      <c r="D18" s="5"/>
       <c r="F18" s="6"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="C19" s="10"/>
+      <c r="D19" s="5"/>
       <c r="F19" s="3"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>44</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="C20" s="10"/>
+      <c r="D20" s="5"/>
       <c r="F20" s="6"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>46</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="C21" s="10"/>
+      <c r="D21" s="5"/>
       <c r="F21" s="3"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>48</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="C22" s="10"/>
+      <c r="D22" s="5"/>
       <c r="F22" s="6"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>50</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C23" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D23" s="5"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>52</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D24" s="5"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>52</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C25" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D25" s="5"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>55</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D26" s="5"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>57</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C27" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D27" s="5"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>59</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D28" s="5"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D29" s="5"/>

--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{131F08C0-98E4-4F7D-9D2A-94BC7D486ACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F69317B-70F5-4C52-9298-C220526679DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="56">
   <si>
     <t>ERRO</t>
   </si>
@@ -62,133 +62,151 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>janaina.rocha@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12997341800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+    <t>daniel.lourenco@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13399435200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
   </si>
   <si>
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>douglas.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13336666300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>crislaine.trindade@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12915132100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12934987200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>matheus.gomes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13398514300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>gleison.ferreira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13396009300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>sonia.bortoleto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12747874100000 Nota 595 - ERRO PDF retorno</t>
+    <t>rosangela.silva1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13381029100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>daniel.ribeiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13385818000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>tatiany.macedo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13397806300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
   </si>
   <si>
     <t>vanessa.penatti@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13401132800000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>priscila.santana@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-20242597823 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>saulo.santiago@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13368618500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>fabio.ribeiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13363583700000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>josiane.vilarinho@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13401363900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>nathalie.carmo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13396276900000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>eduardo.marques@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13095744300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>roberta.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13034353000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+    <t>Retorno de GO referência-13403488800000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13403593200000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>andreia.brixner@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13194682800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>carla.ventura@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13398630600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>noadia.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13396820600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>claudia.assuncao@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13365288200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>rodrigo.laurito@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13396608600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>gabriela.logrado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13390967300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>graziela.salvioni@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13395005000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>lucas.monteiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13397846200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
   </si>
   <si>
     <t>david.silva2@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13242553500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+    <t>Retorno de GO referência-13398841400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>leticia.bezerra@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13393034500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>lais.xavier@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13394199600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
   </si>
   <si>
     <t>enriete.saucedo@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13395618900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>barbara.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13098378100000 Nota 167 - Retorno Cobrança</t>
+    <t>Retorno de GO referência-13363081900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>ana.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13377281300000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>carolina.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13381953800000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>aline.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12858168500000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13173884900000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>daniela.santos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13310163600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
   </si>
   <si>
     <t>carlos.neves@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12489483600000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12544900100000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12629853000000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12777709400000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12846013400000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13038448000000 Nota 242 - Retorno Cobrança</t>
+    <t>Retorno de GO referência-11895004900000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12330661600000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12383611900000 Nota 242 - Retorno Cobrança</t>
   </si>
 </sst>
 </file>
@@ -673,10 +691,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>9</v>
@@ -688,10 +706,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>9</v>
@@ -703,7 +721,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>18</v>
@@ -913,10 +931,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>9</v>
@@ -928,10 +946,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>9</v>
@@ -943,10 +961,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C23" t="s">
         <v>9</v>
@@ -957,10 +975,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C24" t="s">
         <v>9</v>
@@ -971,10 +989,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C25" t="s">
         <v>9</v>
@@ -984,10 +1002,32 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D26" s="5"/>
+      <c r="A26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D27" s="5"/>
+      <c r="A27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D28" s="5"/>

--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D49D0D3-F57C-43D0-91BA-1856EE06395C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{983E9078-F0FD-475D-A32D-C523901A860E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="89">
   <si>
     <t>ERRO</t>
   </si>
@@ -62,136 +62,250 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>johnny.lopes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13402169800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+    <t>kaue.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13401320900000 Nota 595 - ERRO PDF retorno</t>
   </si>
   <si>
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>crislaine.trindade@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13402329700000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>daniel.lourenco@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13405739900000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>diego.vasconcelos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13358916100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>adriano.guerra@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13404157400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+    <t>caroline.falcao@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13399381600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
   </si>
   <si>
     <t>matheus.pereira@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13406431600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>yuri.santos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13396684600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>sonia.bortoleto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13405858200000 Nota 595 - ERRO PDF retorno</t>
+    <t>Retorno de GO referência-13405480600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>juliano.guimaraes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13406943800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>rosthiane.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13387199300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>patricia.farias@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13156833100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>juliana.almeida@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13406598700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13406620100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13407498400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>karina.barros@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13404896000000 Nota 595 - ERRO PDF retorno</t>
   </si>
   <si>
     <t>andreia.brixner@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13405290400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>luciana.mayer@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13406894600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+    <t>Retorno de GO referência-13397603700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>raphael.callado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13407040300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>andre.gouvea@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13405824300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13405865700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>renata.magalhaes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13394688000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>ana.arruda@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13402492200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13406204700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13407742500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>marco.schiabel@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-2394941000182 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>saulo.santiago@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13368618500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
   </si>
   <si>
     <t>claudia.assuncao@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13155150400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>saulo.santiago@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13368556000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>clarissa.cavalli@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13309145100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>fabiane.araujo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13304104200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>eduardo.marques@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13124033400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>david.silva2@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13347702900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13391794900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+    <t>Retorno de GO referência-13402773200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>francieli.becker@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13407799700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>rodrigo.deus@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13013885400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>julianna.printes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13288423000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>monica.prates@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13406616400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>adriano.campos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13406146000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>sonia.nascimento@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13407880000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>gustavo.arruda@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13405852200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>cassia.souza@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13406079700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13408426700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>claudia.malaggi@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13404188200000 Nota 595 - ERRO PDF retorno</t>
   </si>
   <si>
     <t>diego.silva@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-11420811000013 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>joao.neto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13391609700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>rosemeire.faria@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13252404700000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>isabella.lemos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-45936046000155 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+    <t>Retorno de GO referência-13403838800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>daisy.marangoni@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13129271100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>enriete.saucedo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13384390900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>cristiane.lozano@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13094163100004 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>weldja.bozi@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13364850500000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>carolina.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13389983600000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>aline.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12286661300000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>janaina.cazelato@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13386671600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
   </si>
   <si>
     <t>thomaz.jesus@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12448112600000 Nota 167 - Retorno Cobrança</t>
+    <t>Retorno de GO referência-12448063500000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12762122900000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13126600900000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>simone.souza2@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13403868400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>odair.tavares@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13405705800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-20196407753 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
   </si>
 </sst>
 </file>
@@ -736,10 +850,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>23</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>9</v>
@@ -751,10 +865,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>9</v>
@@ -766,10 +880,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>9</v>
@@ -781,10 +895,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>9</v>
@@ -796,10 +910,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>9</v>
@@ -811,10 +925,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>9</v>
@@ -826,10 +940,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>9</v>
@@ -841,10 +955,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>9</v>
@@ -856,10 +970,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>9</v>
@@ -871,10 +985,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>9</v>
@@ -886,10 +1000,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>9</v>
@@ -901,10 +1015,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>9</v>
@@ -916,10 +1030,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>9</v>
@@ -931,10 +1045,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>9</v>
@@ -946,91 +1060,344 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B25" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C23" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D24" s="5"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D25" s="5"/>
+      <c r="C25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D26" s="5"/>
+      <c r="A26" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D27" s="5"/>
+      <c r="A27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D28" s="5"/>
+      <c r="A28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D29" s="5"/>
+      <c r="A29" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C29" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D30" s="5"/>
+      <c r="A30" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D31" s="5"/>
+      <c r="A31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D32" s="5"/>
-    </row>
-    <row r="33" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D33" s="5"/>
-    </row>
-    <row r="34" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D34" s="5"/>
-    </row>
-    <row r="35" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D35" s="5"/>
-    </row>
-    <row r="36" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D36" s="5"/>
-    </row>
-    <row r="37" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D37" s="5"/>
-    </row>
-    <row r="38" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D38" s="5"/>
-    </row>
-    <row r="39" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D39" s="5"/>
-    </row>
-    <row r="40" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D40" s="5"/>
-    </row>
-    <row r="41" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D41" s="5"/>
-    </row>
-    <row r="42" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D42" s="5"/>
-    </row>
-    <row r="43" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D43" s="5"/>
-    </row>
-    <row r="44" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D44" s="5"/>
-    </row>
-    <row r="45" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D45" s="5"/>
-    </row>
-    <row r="46" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D46" s="5"/>
-    </row>
-    <row r="47" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>74</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C38" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>78</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>80</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>80</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C42" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>80</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C43" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>84</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C44" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>86</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C45" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>84</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C46" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D47" s="5"/>
     </row>
-    <row r="48" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D48" s="5"/>
     </row>
   </sheetData>

--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE1E9594-9324-43FF-A0C6-BD1A308AC88B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4C0400F-5996-443A-96A6-8BDE1CCCBF72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="42">
   <si>
     <t>ERRO</t>
   </si>
@@ -60,6 +60,111 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>laiza.quintal@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13131578300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
+  </si>
+  <si>
+    <t>jaciely.dias@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13172691300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>douglas.morais@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13066218900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>raquel.sech@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13372948000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>samuel.martins@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13232041700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>flavio.cesar@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13230181100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>tatiana.monis@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13392026000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>afonso.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13402309500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>leandro.gonzaga@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13095726600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>herbert.goncalves@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13419632300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>rodrigo.laurito@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-22566515000196 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>josiane.vilarinho@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13406788700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>adriano.campos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13419350500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>rodrigo.amorim@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13068937100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>dayane.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13124231300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>cristiane.lozano@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13400063800000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>lucidene.santana@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13419933000000 Nota 472 - Reentrada OK Produto</t>
   </si>
 </sst>
 </file>
@@ -499,286 +604,356 @@
       </c>
     </row>
     <row r="2" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="8"/>
+      <c r="A2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="D2" s="5" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="5"/>
     </row>
     <row r="3" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="8"/>
+      <c r="A3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="D3" s="5" t="s">
         <v>6</v>
       </c>
       <c r="E3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="8"/>
+      <c r="A4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="D4" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C5" s="10"/>
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>9</v>
+      </c>
       <c r="D5" s="5" t="s">
         <v>6</v>
       </c>
       <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C6" s="10"/>
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>9</v>
+      </c>
       <c r="D6" s="5" t="s">
         <v>6</v>
       </c>
       <c r="F6" s="6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C7" s="10"/>
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>9</v>
+      </c>
       <c r="D7" s="5" t="s">
         <v>6</v>
       </c>
       <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C8" s="10"/>
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>9</v>
+      </c>
       <c r="D8" s="5" t="s">
         <v>6</v>
       </c>
       <c r="F8" s="6"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C9" s="10"/>
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>9</v>
+      </c>
       <c r="D9" s="5" t="s">
         <v>6</v>
       </c>
       <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C10" s="10"/>
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>9</v>
+      </c>
       <c r="D10" s="5" t="s">
         <v>6</v>
       </c>
       <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C11" s="10"/>
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>9</v>
+      </c>
       <c r="D11" s="5" t="s">
         <v>6</v>
       </c>
       <c r="F11" s="3"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C12" s="10"/>
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>9</v>
+      </c>
       <c r="D12" s="5" t="s">
         <v>6</v>
       </c>
       <c r="F12" s="6"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C13" s="10"/>
+      <c r="A13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>9</v>
+      </c>
       <c r="D13" s="5" t="s">
         <v>6</v>
       </c>
       <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C14" s="10"/>
+      <c r="A14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>9</v>
+      </c>
       <c r="D14" s="5" t="s">
         <v>6</v>
       </c>
       <c r="F14" s="6"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C15" s="10"/>
+      <c r="A15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>9</v>
+      </c>
       <c r="D15" s="5" t="s">
         <v>6</v>
       </c>
       <c r="F15" s="3"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C16" s="10"/>
+      <c r="A16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>9</v>
+      </c>
       <c r="D16" s="5" t="s">
         <v>6</v>
       </c>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C17" s="10"/>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>9</v>
+      </c>
       <c r="D17" s="5" t="s">
         <v>6</v>
       </c>
       <c r="F17" s="3"/>
     </row>
-    <row r="18" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C18" s="10"/>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>9</v>
+      </c>
       <c r="D18" s="5" t="s">
         <v>6</v>
       </c>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C19" s="10"/>
-      <c r="D19" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D19" s="5"/>
       <c r="F19" s="3"/>
     </row>
-    <row r="20" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C20" s="10"/>
-      <c r="D20" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D20" s="5"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C21" s="10"/>
-      <c r="D21" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D21" s="5"/>
       <c r="F21" s="3"/>
     </row>
-    <row r="22" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C22" s="10"/>
-      <c r="D22" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D22" s="5"/>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D23" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D24" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D25" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D26" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D27" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D28" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D29" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D30" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D31" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D32" s="5" t="s">
-        <v>6</v>
-      </c>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D23" s="5"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D24" s="5"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D25" s="5"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D26" s="5"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D27" s="5"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D28" s="5"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D29" s="5"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D30" s="5"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D31" s="5"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D32" s="5"/>
     </row>
     <row r="33" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D33" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D33" s="5"/>
     </row>
     <row r="34" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D34" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D34" s="5"/>
     </row>
     <row r="35" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D35" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D35" s="5"/>
     </row>
     <row r="36" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D36" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D36" s="5"/>
     </row>
     <row r="37" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D37" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D37" s="5"/>
     </row>
     <row r="38" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D38" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D38" s="5"/>
     </row>
     <row r="39" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D39" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D39" s="5"/>
     </row>
     <row r="40" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D40" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D40" s="5"/>
     </row>
     <row r="41" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D41" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D41" s="5"/>
     </row>
     <row r="42" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D42" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D42" s="5"/>
     </row>
     <row r="43" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D43" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D43" s="5"/>
     </row>
     <row r="44" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D44" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D44" s="5"/>
     </row>
     <row r="45" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D45" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D45" s="5"/>
     </row>
     <row r="46" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D46" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D46" s="5"/>
     </row>
     <row r="47" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D47" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D47" s="5"/>
     </row>
     <row r="48" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D48" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D48" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4C0400F-5996-443A-96A6-8BDE1CCCBF72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{322040F9-96C8-4E28-9F34-DE003B275859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="31">
   <si>
     <t>ERRO</t>
   </si>
@@ -62,109 +62,76 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>laiza.quintal@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13131578300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+    <t>denise.nogueira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-49906914000105 Nota 242 - Retorno Cobrança</t>
   </si>
   <si>
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>jaciely.dias@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13172691300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>douglas.morais@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13066218900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>raquel.sech@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13372948000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>samuel.martins@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13232041700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>flavio.cesar@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13230181100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>tatiana.monis@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13392026000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>afonso.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13402309500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>leandro.gonzaga@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13095726600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>herbert.goncalves@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13419632300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>rodrigo.laurito@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-22566515000196 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>josiane.vilarinho@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13406788700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>adriano.campos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13419350500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>rodrigo.amorim@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13068937100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>dayane.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13124231300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+    <t>kaue.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13353768700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>noadia.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13399847400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>rosilene.nogueira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13408929600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>gustavo.arruda@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13415868900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>raullison.castro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12917291800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>geiza.vinand@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13210048800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
   </si>
   <si>
     <t>cristiane.lozano@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13400063800000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>lucidene.santana@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13419933000000 Nota 472 - Reentrada OK Produto</t>
+    <t>Retorno de GO referência-13094446600000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>weldja.bozi@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13196305800000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13418939100000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>anderson.menezes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11468249700000 Nota 742 - Prêmio</t>
+  </si>
+  <si>
+    <t>ana.carneiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-43627355000118 Nota 242 - Retorno Cobrança</t>
   </si>
 </sst>
 </file>
@@ -739,10 +706,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>26</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>27</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>9</v>
@@ -754,10 +721,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>29</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>9</v>
@@ -769,11 +736,11 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>31</v>
-      </c>
       <c r="C13" s="10" t="s">
         <v>9</v>
       </c>
@@ -783,128 +750,78 @@
       <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="C14" s="10"/>
+      <c r="D14" s="5"/>
       <c r="F14" s="6"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="C15" s="10"/>
+      <c r="D15" s="5"/>
       <c r="F15" s="3"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="5"/>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>6</v>
-      </c>
+    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C17" s="10"/>
+      <c r="D17" s="5"/>
       <c r="F17" s="3"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>6</v>
-      </c>
+    <row r="18" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C18" s="10"/>
+      <c r="D18" s="5"/>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C19" s="10"/>
       <c r="D19" s="5"/>
       <c r="F19" s="3"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="10"/>
       <c r="D20" s="5"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="10"/>
       <c r="D21" s="5"/>
       <c r="F21" s="3"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="10"/>
       <c r="D22" s="5"/>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D23" s="5"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D24" s="5"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D25" s="5"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D26" s="5"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D27" s="5"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D28" s="5"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D29" s="5"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D30" s="5"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D31" s="5"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D32" s="5"/>
     </row>
     <row r="33" spans="4:4" x14ac:dyDescent="0.25">

--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F85D2B89-E0E9-474D-8FEA-43B7496042B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{707C20CF-3EA2-4C5D-8C1B-92DB0B6841B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="102">
   <si>
     <t>ERRO</t>
   </si>
@@ -213,6 +213,138 @@
   </si>
   <si>
     <t>Retorno de GO referência-13079244800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>matheus.pereira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13471289700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13469655300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>andre.gouvea@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13248645300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>luciana.belisario@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13281885100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13281893400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>monica.prates@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13435013200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>rosilene.nogueira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13485848800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>diogo.junior@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13477010900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>priscila.rubio@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13478844100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>dyan.leal@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13462472500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>raullison.castro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13478376900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>cristiane.silva1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13250150000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>bruna.carneiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13480748700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>eudmila.tassara@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13426636500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>carolina.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13056194200000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>rosemeire.faria@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13401323900000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13462168800000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13465741400000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13465857300000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13466068000000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13466224700000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13466359100000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13467079800000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13467147700000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13468478100000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>carlos.neves@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12371199000000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12712428600000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12792760500000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13079922500000 Nota 242 - Retorno Cobrança</t>
   </si>
 </sst>
 </file>
@@ -621,7 +753,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.42578125" customWidth="1" collapsed="1"/>
@@ -697,10 +829,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>9</v>
@@ -715,7 +847,7 @@
         <v>13</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>9</v>
@@ -727,10 +859,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>9</v>
@@ -742,10 +874,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>9</v>
@@ -757,10 +889,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>9</v>
@@ -772,10 +904,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>9</v>
@@ -787,10 +919,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>9</v>
@@ -802,10 +934,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>9</v>
@@ -817,10 +949,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>9</v>
@@ -832,10 +964,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>9</v>
@@ -847,10 +979,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>9</v>
@@ -862,10 +994,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>9</v>
@@ -877,10 +1009,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>9</v>
@@ -892,10 +1024,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>9</v>
@@ -907,10 +1039,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>9</v>
@@ -922,10 +1054,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>9</v>
@@ -937,10 +1069,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>9</v>
@@ -952,10 +1084,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>9</v>
@@ -967,10 +1099,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="C23" t="s">
         <v>9</v>
@@ -981,10 +1113,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="C24" t="s">
         <v>9</v>
@@ -995,10 +1127,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="C25" t="s">
         <v>9</v>
@@ -1009,10 +1141,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="C26" t="s">
         <v>9</v>
@@ -1023,10 +1155,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="C27" t="s">
         <v>9</v>
@@ -1037,77 +1169,423 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>78</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>80</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C34" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>82</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C35" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>84</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C36" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>86</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>84</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C38" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C39" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C42" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C43" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C44" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C45" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>84</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>84</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C47" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>47</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C48" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>49</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C49" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>51</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C50" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>51</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C51" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>54</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C52" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B53" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D29" s="5"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D30" s="5"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D31" s="5"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D32" s="5"/>
-    </row>
-    <row r="33" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D33" s="5"/>
-    </row>
-    <row r="34" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D34" s="5"/>
-    </row>
-    <row r="35" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D35" s="5"/>
-    </row>
-    <row r="36" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D36" s="5"/>
-    </row>
-    <row r="37" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D37" s="5"/>
-    </row>
-    <row r="38" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D38" s="5"/>
-    </row>
-    <row r="39" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D39" s="5"/>
-    </row>
-    <row r="40" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D40" s="5"/>
-    </row>
-    <row r="41" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D41" s="5"/>
-    </row>
-    <row r="42" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D42" s="5"/>
-    </row>
-    <row r="43" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D43" s="5"/>
-    </row>
-    <row r="44" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D44" s="5"/>
-    </row>
-    <row r="45" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D45" s="5"/>
-    </row>
-    <row r="46" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D46" s="5"/>
-    </row>
-    <row r="47" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D47" s="5"/>
-    </row>
-    <row r="48" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D48" s="5"/>
+      <c r="C53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>97</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>97</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C55" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>97</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C56" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>97</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C57" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -1122,31 +1600,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ECF9874-EDD0-4B43-8017-C343DACF060B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ACE8C15-7D0B-474E-B949-2945D2BB0F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F7DEB0-8222-4DA4-9636-B5077762E3EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="74">
   <si>
     <t>ERRO</t>
   </si>
@@ -62,196 +62,205 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>janaina.rocha@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13476468600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>bruno.rosa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13299421000107 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>daniela.leal@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13500689200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>gleison.ferreira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13508879400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>priscila.santana@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13507802400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>wagner.simon@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13473465300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>rafael.petrin@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13515559500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>eliane.fernandes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13512658400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>andreza.libanore@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13502836600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>monica.betoni@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13506623600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>andreia.cardias@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13252005600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>rosilene.nogueira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-00988040301 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>gabriela.logrado@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13117896100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13507565500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13512871300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13512940500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13513029200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13513314100000 Nota 595 - ERRO PDF etorno Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13513453600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13513819100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13513848900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13514116500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13514179800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13514300400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13514469800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13514489800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13514582000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>geiza.vinand@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13202410300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>leandro.susanj@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13511441900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>thays.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13514164300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
     <t>ana.rodrigues@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13096658800000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>carolina.lima@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13217455600000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
     <t>cristiane.lozano@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13469166700000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13493212200000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13497946800000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13500881700000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>lucidene.santana@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13501896300000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13504913300000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13507282600000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>claudenice.barbosa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13513359700000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>alan.david@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12827964100013 Nota 167 - Retorno Cobrança</t>
+    <t>bruna.silva1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13513238100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>douglas.morais@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13400925300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>eliana.pedroso@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13517610400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>adriano.guerra@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13459147100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>rosiane.honorato@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13164200900000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>kaue.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13508436200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>rosthiane.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13514664500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>daniel.iarrocheski@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-04124799900 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>kaue.medeiros@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13513523600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>yuri.santos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-45095299100 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>elisangela.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13505780300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>raphael.callado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13516408400000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>claudia.pires@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13515969300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>monica.prates@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-79330886515 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>renata.melo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13204126800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>luciene.fernandes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13508036100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>daniele.beck@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13516350500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>rosana.teixeira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13506627600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>raullison.castro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13344986800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>gabriel.nascimento@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13477536200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>claudia.malaggi@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13517231000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>andrea.farias1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13518317100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>leticia.bezerra@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13502910600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>lais.xavier@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13504876100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>diego.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13514067500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>rosemeire.faria@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13270664700000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13498482500000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>marli.rocha@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13501873300000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13502837700000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13511441900000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>karla.cunha@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-40703775812 Nota 531 - Alteração ou correção dados cadastrais</t>
+  </si>
+  <si>
+    <t>thaiana.felipe@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13153431600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>odair.tavares@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-45928137826 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>simone.sa@allianz.com.br</t>
   </si>
 </sst>
 </file>
@@ -660,7 +669,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.42578125" customWidth="1" collapsed="1"/>
@@ -692,13 +701,13 @@
     </row>
     <row r="2" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>6</v>
@@ -707,13 +716,13 @@
     </row>
     <row r="3" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>6</v>
@@ -722,13 +731,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>6</v>
@@ -736,13 +745,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>6</v>
@@ -751,13 +760,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>6</v>
@@ -766,13 +775,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>6</v>
@@ -781,13 +790,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>6</v>
@@ -796,13 +805,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>6</v>
@@ -811,13 +820,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>6</v>
@@ -826,13 +835,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>6</v>
@@ -841,13 +850,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>6</v>
@@ -856,13 +865,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>6</v>
@@ -871,13 +880,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>6</v>
@@ -886,13 +895,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>6</v>
@@ -901,13 +910,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>6</v>
@@ -916,13 +925,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>6</v>
@@ -931,13 +940,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>6</v>
@@ -946,13 +955,13 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>6</v>
@@ -961,13 +970,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>6</v>
@@ -976,13 +985,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>6</v>
@@ -991,13 +1000,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>6</v>
@@ -1006,13 +1015,13 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C23" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>6</v>
@@ -1020,13 +1029,13 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>6</v>
@@ -1034,13 +1043,13 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="C25" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>6</v>
@@ -1048,13 +1057,13 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="C26" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>6</v>
@@ -1062,13 +1071,13 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="C27" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>6</v>
@@ -1076,13 +1085,13 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="C28" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>6</v>
@@ -1090,13 +1099,13 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="C29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>6</v>
@@ -1104,13 +1113,13 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="C30" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>6</v>
@@ -1118,13 +1127,13 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="C31" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>6</v>
@@ -1132,13 +1141,13 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="C32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>6</v>
@@ -1146,13 +1155,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="C33" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>6</v>
@@ -1160,13 +1169,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="C34" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>6</v>
@@ -1174,113 +1183,15 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="C35" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>56</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C36" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>58</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>63</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C38" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>54</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C39" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>63</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C40" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>67</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C41" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>69</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C42" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="5" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1297,31 +1208,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ECF9874-EDD0-4B43-8017-C343DACF060B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7699E7-09DD-4C81-B271-7B79BFC65A0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C2986D6-86A0-4BFF-B1D5-8655C69F78DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24120" yWindow="1770" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="26640" yWindow="1725" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RetornoGo" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="51">
   <si>
     <t>ERRO</t>
   </si>
@@ -62,241 +62,136 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>crislaine.trindade@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13517355200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>lilian.sudati@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13535906700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>danielle.nascimento@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13537179000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>renato.lopes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13293458200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>juliano.guimaraes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13537553200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>daniel.ribeiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13040853100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>daiane.soares@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13534397000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>bruno.rosa@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13535176100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>gisele.cardoso1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13201946000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>erica.cassandre@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13242760100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13532836000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>mayara.sampaio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13529621000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>andre.gouvea@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13534494100000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>nilcea.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13536212300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>flavio.funke@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13520264100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13536366000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>monica.prates@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13537873600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>luciene.fernandes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13532794500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>priscila.rubio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13420967600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>daniela.gois@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13370029200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
     <t>raullison.castro@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13535241700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
     <t>gabriela.logrado@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13527087800000 Nota 595 - ERRO PDF Retornobe</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13529208100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13530458700000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13533042000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13533650000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13535655300000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13536089500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13536712600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13536814900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13537068100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13537308500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13539173300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>geiza.vinand@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13534446800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>patricia.soares@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13534155800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13535360100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>daisy.marangoni@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13440438600000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>marli.rocha@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13161229500000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>ana.rodrigues@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13521690000000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>carla.catalani@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13514231900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>adilson.rodrigues@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13374984200000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>ana.carneiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-27389845000177 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>carlos.neves@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11645972300000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12330661600000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12629853000000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12784998900000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12786851800000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12796063500000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12843305100000 Nota 242 - Retorno Cobrança</t>
+    <t>filipe.pereira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13538907400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>claudia.ribeiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13525184900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>patricia.farias@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13535055800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13424468500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>juliana.diniz@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13516177500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>caroline.wojciechowski@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13326666000000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13527466900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>luciana.mayer@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13531747700000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>julianna.printes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13534304100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>pamela.burige@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13483956700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13538108300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13531829200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13534185300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13534665500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13536091600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13536207900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13537690800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13537691400000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13538051200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13538133400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13538184300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13538570800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13538957600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13539000200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13539207500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13539335100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>eduardo.santos1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13465413000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>weldja.bozi@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13469995400000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>alexia.goncalves@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13532417700000 Nota 595 - ERRO PDF retorno</t>
   </si>
 </sst>
 </file>
@@ -737,13 +632,13 @@
     </row>
     <row r="2" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>6</v>
@@ -752,13 +647,13 @@
     </row>
     <row r="3" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>6</v>
@@ -767,13 +662,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>6</v>
@@ -781,13 +676,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>6</v>
@@ -796,13 +691,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>6</v>
@@ -811,13 +706,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>6</v>
@@ -829,10 +724,10 @@
         <v>20</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>6</v>
@@ -841,13 +736,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>6</v>
@@ -856,13 +751,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>6</v>
@@ -871,13 +766,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>6</v>
@@ -886,13 +781,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>6</v>
@@ -901,13 +796,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>6</v>
@@ -916,13 +811,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>32</v>
-      </c>
       <c r="C14" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>6</v>
@@ -931,13 +826,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>6</v>
@@ -946,13 +841,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>6</v>
@@ -961,13 +856,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>6</v>
@@ -976,13 +871,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>6</v>
@@ -991,13 +886,13 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>6</v>
@@ -1006,13 +901,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>6</v>
@@ -1021,13 +916,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>6</v>
@@ -1036,13 +931,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>6</v>
@@ -1051,13 +946,13 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>6</v>
@@ -1065,13 +960,13 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>6</v>
@@ -1079,13 +974,13 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>6</v>
@@ -1093,13 +988,13 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>6</v>
@@ -1107,13 +1002,13 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>6</v>
@@ -1121,13 +1016,13 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>6</v>
@@ -1135,13 +1030,13 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>55</v>
-      </c>
       <c r="C29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>6</v>
@@ -1149,297 +1044,77 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>48</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C31" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D31" s="5"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>48</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C32" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>48</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C33" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>48</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C34" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>61</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C35" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>63</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C36" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>63</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>66</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C38" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>68</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C39" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>70</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C40" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>72</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C41" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>74</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C42" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>76</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C43" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>78</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C44" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>78</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C45" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>78</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C46" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>78</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C47" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>78</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C48" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>78</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C49" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>78</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C50" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D32" s="5"/>
+    </row>
+    <row r="33" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D33" s="5"/>
+    </row>
+    <row r="34" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D34" s="5"/>
+    </row>
+    <row r="35" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D35" s="5"/>
+    </row>
+    <row r="36" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D36" s="5"/>
+    </row>
+    <row r="37" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D37" s="5"/>
+    </row>
+    <row r="38" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D38" s="5"/>
+    </row>
+    <row r="39" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D39" s="5"/>
+    </row>
+    <row r="40" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D40" s="5"/>
+    </row>
+    <row r="41" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D41" s="5"/>
+    </row>
+    <row r="42" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D42" s="5"/>
+    </row>
+    <row r="43" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D43" s="5"/>
+    </row>
+    <row r="44" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D44" s="5"/>
+    </row>
+    <row r="45" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D45" s="5"/>
+    </row>
+    <row r="46" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D46" s="5"/>
+    </row>
+    <row r="47" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D47" s="5"/>
+    </row>
+    <row r="48" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D48" s="5"/>
+    </row>
+    <row r="49" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D49" s="5"/>
+    </row>
+    <row r="50" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D50" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -1454,31 +1129,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ECF9874-EDD0-4B43-8017-C343DACF060B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C2986D6-86A0-4BFF-B1D5-8655C69F78DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC4C0C8-52B7-4AC6-831C-1B806A94B980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26640" yWindow="1725" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RetornoGo" sheetId="2" r:id="rId1"/>
@@ -1129,31 +1129,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ECF9874-EDD0-4B43-8017-C343DACF060B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ECF9874-EDD0-4B43-8017-C343DACF060B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC4C0C8-52B7-4AC6-831C-1B806A94B980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EEA7465-DB63-4BEA-982D-9A4D9AFA6016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RetornoGo" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="65">
   <si>
     <t>ERRO</t>
   </si>
@@ -62,136 +62,178 @@
     <t>Processar</t>
   </si>
   <si>
+    <t>mislene.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13036609700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>bruno.rosa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>raullison.castro@allianz.com.br</t>
+    <t>rodrigo.kuguyama@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11807720900000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>nilcea.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13541947500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>lucas.almeida@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13543705700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>claudia.gomes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13537906100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>leandro.machado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-45138126000165 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-62556793000187 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>andreza.libanore@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13545036500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>karla.ribeiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13540629500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>renato.faillace@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13543412500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>priscila.rubio@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13075766300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
   </si>
   <si>
     <t>gabriela.logrado@allianz.com.br</t>
   </si>
   <si>
-    <t>filipe.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13538907400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>claudia.ribeiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13525184900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>patricia.farias@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13535055800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13424468500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>juliana.diniz@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13516177500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>caroline.wojciechowski@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13326666000000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13527466900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>luciana.mayer@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13531747700000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>julianna.printes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13534304100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>pamela.burige@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13483956700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13538108300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13531829200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13534185300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13534665500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13536091600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13536207900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13537690800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13537691400000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13538051200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13538133400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13538184300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13538570800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13538957600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13539000200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13539207500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13539335100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>eduardo.santos1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13465413000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+    <t>Retorno de GO referência-13166560900000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13537331900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13537591400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13537740500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13539863200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13540468800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13540726100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13541275400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>aline.madeira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13542871600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13544363900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>adriano.guerra@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13529848100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>ivana.freitas@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13542144000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>wagner.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13531890200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>eudmila.tassara@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13542762200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>joao.neto@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13538505800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>ana.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13226050100000 Nota 167 - Retorno Cobrança</t>
   </si>
   <si>
     <t>weldja.bozi@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13469995400000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>alexia.goncalves@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13532417700000 Nota 595 - ERRO PDF retorno</t>
+    <t>Retorno de GO referência-13342760200000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13458936700000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>carolina.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13529848100000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>carlos.neves@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11672287100000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12246396200000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12246736700000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12844934100000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>graziela.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13313468200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
   </si>
 </sst>
 </file>
@@ -600,7 +642,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.42578125" customWidth="1" collapsed="1"/>
@@ -632,13 +674,13 @@
     </row>
     <row r="2" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>6</v>
@@ -647,13 +689,13 @@
     </row>
     <row r="3" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>6</v>
@@ -662,13 +704,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>6</v>
@@ -676,13 +718,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>6</v>
@@ -691,13 +733,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>6</v>
@@ -706,13 +748,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>6</v>
@@ -721,13 +763,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>22</v>
-      </c>
       <c r="C8" s="10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>6</v>
@@ -736,13 +778,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>6</v>
@@ -751,13 +793,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>6</v>
@@ -766,13 +808,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>6</v>
@@ -781,13 +823,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>6</v>
@@ -796,13 +838,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>6</v>
@@ -811,13 +853,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>6</v>
@@ -826,13 +868,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>32</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>6</v>
@@ -841,13 +883,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>33</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>6</v>
@@ -856,13 +898,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>34</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>6</v>
@@ -871,13 +913,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>6</v>
@@ -886,13 +928,13 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>36</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>6</v>
@@ -901,13 +943,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>37</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>6</v>
@@ -916,13 +958,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>6</v>
@@ -931,13 +973,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>6</v>
@@ -946,13 +988,13 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>6</v>
@@ -960,13 +1002,13 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>6</v>
@@ -974,13 +1016,13 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>6</v>
@@ -988,13 +1030,13 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C26" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>6</v>
@@ -1002,13 +1044,13 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C27" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>6</v>
@@ -1016,13 +1058,13 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C28" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>6</v>
@@ -1030,13 +1072,13 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C29" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>6</v>
@@ -1044,77 +1086,101 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C30" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D31" s="5"/>
+      <c r="A31" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D32" s="5"/>
-    </row>
-    <row r="33" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D33" s="5"/>
-    </row>
-    <row r="34" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D34" s="5"/>
-    </row>
-    <row r="35" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D35" s="5"/>
-    </row>
-    <row r="36" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D36" s="5"/>
-    </row>
-    <row r="37" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D37" s="5"/>
-    </row>
-    <row r="38" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D38" s="5"/>
-    </row>
-    <row r="39" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D39" s="5"/>
-    </row>
-    <row r="40" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D40" s="5"/>
-    </row>
-    <row r="41" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D41" s="5"/>
-    </row>
-    <row r="42" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D42" s="5"/>
-    </row>
-    <row r="43" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D43" s="5"/>
-    </row>
-    <row r="44" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D44" s="5"/>
-    </row>
-    <row r="45" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D45" s="5"/>
-    </row>
-    <row r="46" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D46" s="5"/>
-    </row>
-    <row r="47" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D47" s="5"/>
-    </row>
-    <row r="48" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D48" s="5"/>
-    </row>
-    <row r="49" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D49" s="5"/>
-    </row>
-    <row r="50" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D50" s="5"/>
+      <c r="A32" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C32" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>58</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>58</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C34" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>58</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C35" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>63</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C36" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EEA7465-DB63-4BEA-982D-9A4D9AFA6016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A4FE68-CE89-4617-B2B3-3E882E392CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RetornoGo" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="38">
   <si>
     <t>ERRO</t>
   </si>
@@ -62,178 +62,97 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>mislene.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13036609700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>rodrigo.kuguyama@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11807720900000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>nilcea.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13541947500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>lucas.almeida@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13543705700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>claudia.gomes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13537906100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>leandro.machado@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-45138126000165 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-62556793000187 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>andreza.libanore@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13545036500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>karla.ribeiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13540629500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>renato.faillace@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13543412500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>priscila.rubio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13075766300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>gabriela.logrado@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13166560900000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13537331900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13537591400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13537740500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13539863200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13540468800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13540726100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13541275400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>aline.madeira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13542871600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13544363900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>adriano.guerra@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13529848100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>ivana.freitas@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13542144000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>wagner.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13531890200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>eudmila.tassara@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13542762200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>joao.neto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13538505800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
     <t>ana.rodrigues@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13226050100000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>weldja.bozi@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13342760200000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13458936700000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
     <t>carolina.lima@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13529848100000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>carlos.neves@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11672287100000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12246396200000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12246736700000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12844934100000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>graziela.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13313468200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+    <t>mariana.dolence@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-73903582972 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>patricia.farias@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13538306000000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>alex.grabowski@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13540298100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>andre.gouvea@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13533799400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>diogo.junior@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13470235200000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>erica.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13533628400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>raullison.castro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13344986800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>betina.carrasco@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13292145500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>laila.steil@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13533933300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13525055800000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13529908400000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>rose.lourenco@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-2038327874 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>ana.costa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-36989720182 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>fabiana.aquino@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-99577895620 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>ana.brito@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13431670600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
   </si>
 </sst>
 </file>
@@ -642,7 +561,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.42578125" customWidth="1" collapsed="1"/>
@@ -674,13 +593,13 @@
     </row>
     <row r="2" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>6</v>
@@ -689,13 +608,13 @@
     </row>
     <row r="3" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>6</v>
@@ -704,13 +623,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>6</v>
@@ -718,13 +637,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>6</v>
@@ -733,13 +652,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>6</v>
@@ -748,13 +667,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>6</v>
@@ -763,13 +682,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>6</v>
@@ -778,13 +697,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>6</v>
@@ -793,13 +712,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>6</v>
@@ -808,13 +727,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>6</v>
@@ -823,13 +742,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>6</v>
@@ -838,13 +757,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>6</v>
@@ -853,13 +772,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>6</v>
@@ -868,13 +787,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>6</v>
@@ -883,304 +802,18 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>6</v>
       </c>
       <c r="F16" s="6"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" s="3"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>29</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" s="6"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" s="3"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" s="6"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" s="3"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" s="6"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>41</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C23" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C25" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>47</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C26" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>49</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C27" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>51</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>53</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C29" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>51</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C30" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>56</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C31" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>58</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C32" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>58</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C33" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>58</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C34" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>58</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C35" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>63</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C36" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -1195,31 +828,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ECF9874-EDD0-4B43-8017-C343DACF060B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A4FE68-CE89-4617-B2B3-3E882E392CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E6EDB74-1066-4BDE-B641-D724A2950FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21270" yWindow="780" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RetornoGo" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="64">
   <si>
     <t>ERRO</t>
   </si>
@@ -65,94 +65,172 @@
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>ana.rodrigues@allianz.com.br</t>
-  </si>
-  <si>
-    <t>carolina.lima@allianz.com.br</t>
-  </si>
-  <si>
-    <t>mariana.dolence@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-73903582972 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>patricia.farias@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13538306000000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
     <t>alex.grabowski@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13540298100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>andre.gouvea@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13533799400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>diogo.junior@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13470235200000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>erica.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13533628400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>raullison.castro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13344986800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>betina.carrasco@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13292145500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>laila.steil@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13533933300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13525055800000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13529908400000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>rose.lourenco@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-2038327874 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>ana.costa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-36989720182 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>fabiana.aquino@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-99577895620 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>ana.brito@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13431670600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+    <t>danielle.nascimento@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13528776000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>adriana.coelho@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13551657200000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>kaue.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13141721200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-41756764000199 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>daiane.soares@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13277478600000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13451320300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>lidiane.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13547019100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>tatiana.monis@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13496807300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>erica.cassandre@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13550836600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>ana.guanais@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13549189000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>julianna.printes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13356332500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>fabiane.araujo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13544364700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>rosilene.nogueira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-48668929000110 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>flavia.costa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13543883100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13551504200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>adriano.campos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-56356048700 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>gabriela.logrado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13529485400000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13542888000000 Nota 595 - ERRO PDF retorno be00856</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13543407000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13546560700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13546910200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13547226200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13548274600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>cristiane.konrad@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13067434900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>rafaela.jeronimo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13400665300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>patricia.soares@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13539487500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>eduardo.santos1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13549104500000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>rodrigo.belisario@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13512126400000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>thomaz.jesus@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12448063500000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12448112600000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13173075400000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>everaldo.cordeiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13534502600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>valeria.ribeiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-94939594904 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
   </si>
 </sst>
 </file>
@@ -561,7 +639,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.42578125" customWidth="1" collapsed="1"/>
@@ -593,10 +671,10 @@
     </row>
     <row r="2" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>10</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>11</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>7</v>
@@ -608,10 +686,10 @@
     </row>
     <row r="3" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>12</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>13</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>7</v>
@@ -623,10 +701,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>14</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>15</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>7</v>
@@ -637,10 +715,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>7</v>
@@ -652,10 +730,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>7</v>
@@ -667,10 +745,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>7</v>
@@ -682,10 +760,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>7</v>
@@ -697,10 +775,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>7</v>
@@ -712,10 +790,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>7</v>
@@ -727,10 +805,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>7</v>
@@ -742,10 +820,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>7</v>
@@ -757,10 +835,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>7</v>
@@ -772,10 +850,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>32</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>33</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>7</v>
@@ -787,10 +865,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>34</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>35</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>7</v>
@@ -802,18 +880,270 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" s="6"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B17" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" s="6"/>
+      <c r="C17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>56</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C32" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C33" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>62</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C34" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -828,31 +1158,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ECF9874-EDD0-4B43-8017-C343DACF060B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ECF9874-EDD0-4B43-8017-C343DACF060B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E6EDB74-1066-4BDE-B641-D724A2950FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F67DB0C1-9053-40E7-B850-C7B14BA844DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21270" yWindow="780" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RetornoGo" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="50">
   <si>
     <t>ERRO</t>
   </si>
@@ -65,172 +65,130 @@
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>alex.grabowski@allianz.com.br</t>
-  </si>
-  <si>
-    <t>danielle.nascimento@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13528776000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>adriana.coelho@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13551657200000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>kaue.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13141721200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-41756764000199 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>daiane.soares@allianz.com.br</t>
-  </si>
-  <si>
     <t>Retorno de GO referência-13277478600000 Nota 167 - Retorno Cobrança</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13451320300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>lidiane.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13547019100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
     <t>tatiana.monis@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13496807300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
     <t>erica.cassandre@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13550836600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>ana.guanais@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13549189000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>julianna.printes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13356332500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>fabiane.araujo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13544364700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>rosilene.nogueira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-48668929000110 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>flavia.costa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13543883100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13551504200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
     <t>adriano.campos@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-56356048700 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>gabriela.logrado@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13529485400000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13542888000000 Nota 595 - ERRO PDF retorno be00856</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13543407000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13546560700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13546910200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13547226200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13548274600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>cristiane.konrad@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13067434900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>rafaela.jeronimo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13400665300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>patricia.soares@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13539487500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>eduardo.santos1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13549104500000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>rodrigo.belisario@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13512126400000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>thomaz.jesus@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12448063500000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12448112600000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13173075400000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>everaldo.cordeiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13534502600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>valeria.ribeiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-94939594904 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+    <t>daniel.lourenco@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13252220000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>matheus.gomes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13548812000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>jessika.pazin@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13539918800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>bruno.castro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13538916800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>priscila.santana@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13551109300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>juliana.diniz@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13534335800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>gisele.cardoso1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13538199400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13546804800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13549369600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>raphael.callado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13551286300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>andre.gouvea@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13221162700000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>mayara.sampaio@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13521493400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>renata.melo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13074672700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13548557800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>betina.carrasco@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13546956500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>adriano.guerra@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13209384100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>jheniffer.emiliano@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13543880000000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>laila.steil@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13527010000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>rosana.pessoa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13534692800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>caio.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13551769300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>mauricio.santo@allianz.com.br</t>
   </si>
 </sst>
 </file>
@@ -639,7 +597,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.42578125" customWidth="1" collapsed="1"/>
@@ -671,10 +629,10 @@
     </row>
     <row r="2" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>7</v>
@@ -686,10 +644,10 @@
     </row>
     <row r="3" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>7</v>
@@ -701,10 +659,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>7</v>
@@ -715,10 +673,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>7</v>
@@ -730,10 +688,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>7</v>
@@ -745,10 +703,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>7</v>
@@ -760,10 +718,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>7</v>
@@ -775,10 +733,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>7</v>
@@ -790,10 +748,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>7</v>
@@ -805,10 +763,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>7</v>
@@ -820,10 +778,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>7</v>
@@ -835,10 +793,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>7</v>
@@ -850,10 +808,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>7</v>
@@ -865,10 +823,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>7</v>
@@ -880,10 +838,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>7</v>
@@ -895,10 +853,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C17" t="s">
         <v>7</v>
@@ -909,10 +867,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C18" t="s">
         <v>7</v>
@@ -923,10 +881,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
         <v>7</v>
@@ -937,10 +895,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C20" t="s">
         <v>7</v>
@@ -951,10 +909,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C21" t="s">
         <v>7</v>
@@ -965,183 +923,15 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="C22" t="s">
         <v>7</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" t="s">
-        <v>7</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>48</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C26" t="s">
-        <v>7</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>50</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C27" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>52</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C28" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>54</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C29" t="s">
-        <v>7</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>56</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>56</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C31" t="s">
-        <v>7</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>56</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C32" t="s">
-        <v>7</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>60</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C33" t="s">
-        <v>7</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>62</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C34" t="s">
-        <v>7</v>
-      </c>
-      <c r="D34" s="5" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1158,31 +948,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ECF9874-EDD0-4B43-8017-C343DACF060B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F67DB0C1-9053-40E7-B850-C7B14BA844DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED2B494-EC9C-4C91-810D-E11D606A5F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="77">
   <si>
     <t>ERRO</t>
   </si>
@@ -65,130 +65,211 @@
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13277478600000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>tatiana.monis@allianz.com.br</t>
-  </si>
-  <si>
-    <t>erica.cassandre@allianz.com.br</t>
-  </si>
-  <si>
-    <t>adriano.campos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>daniel.lourenco@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13252220000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>matheus.gomes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13548812000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>jessika.pazin@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13539918800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>bruno.castro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13538916800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>priscila.santana@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13551109300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
     <t>juliana.diniz@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13534335800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
     <t>gisele.cardoso1@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13538199400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13546804800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13549369600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>raphael.callado@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13551286300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>andre.gouvea@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13221162700000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>mayara.sampaio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13521493400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>renata.melo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13074672700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13548557800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
     <t>betina.carrasco@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13546956500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>adriano.guerra@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13209384100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>jheniffer.emiliano@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13543880000000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
     <t>laila.steil@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13527010000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>rosana.pessoa@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13534692800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>caio.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13551769300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>mauricio.santo@allianz.com.br</t>
+    <t>crislaine.trindade@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13549408100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13551570600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>isabel.cit@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13540108000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>daiane.soares@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13550804900000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>bruno.rosa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13555849400000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13464655600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13516177500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13525296100000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13547064600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>silvia.taschetti@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13318368200000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>afonso.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13246648100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>andriele.pala@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13542798000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>danilo.ruas@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13553974300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>viviane.corbari@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13556160200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>shirley.almeida@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13538794600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>renato.faillace@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13555244000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>priscila.rubio@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13100175800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13446636900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>daniele.beck@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13550962300000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>gabriela.logrado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13547890600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13548168100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13550046900000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13550109200000 Nota 595 - ERRO PDF pdf</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13550654200000 Nota 595 - ERRO PDF PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13551757200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13552168500000 Nota 595 - ERRO PDF PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13554448300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13293169800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>bruna.carneiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13542520300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13544783400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>maria.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13553402900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13554148600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>thays.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13554324700000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13554657200000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13548868200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>ivone.jesus@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13119406600000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>claudenice.barbosa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13189304500000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13541150000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>luana.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13457444400000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13457463300000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>daniella.azevedo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13213979600000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>simone.santos1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-80693091991 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
   </si>
 </sst>
 </file>
@@ -597,7 +678,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.42578125" customWidth="1" collapsed="1"/>
@@ -629,10 +710,10 @@
     </row>
     <row r="2" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>7</v>
@@ -644,7 +725,7 @@
     </row>
     <row r="3" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>15</v>
@@ -703,10 +784,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>23</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>7</v>
@@ -718,10 +799,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>7</v>
@@ -733,10 +814,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>7</v>
@@ -751,7 +832,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>7</v>
@@ -763,10 +844,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>7</v>
@@ -778,10 +859,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>7</v>
@@ -793,10 +874,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>7</v>
@@ -808,10 +889,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>7</v>
@@ -823,10 +904,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>7</v>
@@ -838,10 +919,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>7</v>
@@ -853,10 +934,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>39</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>40</v>
       </c>
       <c r="C17" t="s">
         <v>7</v>
@@ -867,10 +948,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>42</v>
       </c>
       <c r="C18" t="s">
         <v>7</v>
@@ -881,10 +962,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C19" t="s">
         <v>7</v>
@@ -895,10 +976,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
         <v>7</v>
@@ -909,10 +990,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C21" t="s">
         <v>7</v>
@@ -923,15 +1004,309 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" s="5" t="s">
+      <c r="C24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>10</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>55</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C32" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>58</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C33" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C34" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>61</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C35" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C36" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>65</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>67</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C38" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>12</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C39" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>70</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>70</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C41" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>73</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C42" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>75</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C43" t="s">
+        <v>7</v>
+      </c>
+      <c r="D43" s="5" t="s">
         <v>6</v>
       </c>
     </row>
@@ -948,31 +1323,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ECF9874-EDD0-4B43-8017-C343DACF060B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ECF9874-EDD0-4B43-8017-C343DACF060B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED2B494-EC9C-4C91-810D-E11D606A5F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C3A336E-254E-4B41-B759-61FCFE4DFC54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="60">
   <si>
     <t>ERRO</t>
   </si>
@@ -65,211 +65,160 @@
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>juliana.diniz@allianz.com.br</t>
-  </si>
-  <si>
-    <t>gisele.cardoso1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>betina.carrasco@allianz.com.br</t>
-  </si>
-  <si>
     <t>laila.steil@allianz.com.br</t>
   </si>
   <si>
-    <t>rosana.pessoa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>crislaine.trindade@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13549408100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13551570600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>isabel.cit@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13540108000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>daiane.soares@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13550804900000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>bruno.rosa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13555849400000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13464655600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13516177500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13525296100000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13547064600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>silvia.taschetti@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13318368200000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>afonso.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13246648100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>andriele.pala@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13542798000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
     <t>danilo.ruas@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13553974300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>viviane.corbari@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13556160200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>shirley.almeida@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13538794600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>renato.faillace@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13555244000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>priscila.rubio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13100175800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13446636900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>daniele.beck@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13550962300000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>gabriela.logrado@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13547890600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13548168100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13550046900000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13550109200000 Nota 595 - ERRO PDF pdf</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13550654200000 Nota 595 - ERRO PDF PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13551757200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13552168500000 Nota 595 - ERRO PDF PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13554448300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13293169800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>bruna.carneiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13542520300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13544783400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>maria.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13553402900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13554148600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>thays.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13554324700000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13554657200000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13548868200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>ivone.jesus@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13119406600000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
     <t>claudenice.barbosa@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13189304500000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13541150000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>luana.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13457444400000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13457463300000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>daniella.azevedo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13213979600000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>simone.santos1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-80693091991 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+    <t>eliana.pedroso@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13545775100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13546732300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>daniel.lourenco@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13550001600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>matheus.pereira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13538898100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>mariana.dolence@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13554077400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>fabio.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13514076200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>gleison.ferreira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13384026100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>mayara.sampaio@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13556245800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13546049500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>marco.schiabel@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13552257600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>aline.carpes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13215826300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>daniel.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13539678800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>fabio.ribeiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13556204800000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>flavia.costa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13553068900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13554058000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13556959100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>lucas.monteiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13556213700000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>lais.xavier@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13030334900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>eudmila.tassara@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13493109200000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>eduardo.santos1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13551810800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>enriete.saucedo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13555814200000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13558325600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>cristiane.lozano@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13546732300000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>laerte.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11990175200000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>thomaz.jesus@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11105147000000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>viviane.duarte@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13328788400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>kelli.santos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13362874600000 Nota 595 - ERRO PDF Retorno</t>
   </si>
 </sst>
 </file>
@@ -678,7 +627,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.42578125" customWidth="1" collapsed="1"/>
@@ -710,10 +659,10 @@
     </row>
     <row r="2" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>7</v>
@@ -725,10 +674,10 @@
     </row>
     <row r="3" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>13</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>15</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>7</v>
@@ -740,10 +689,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>7</v>
@@ -754,10 +703,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>7</v>
@@ -769,10 +718,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>7</v>
@@ -784,10 +733,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>7</v>
@@ -799,7 +748,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>23</v>
@@ -814,10 +763,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>7</v>
@@ -832,7 +781,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>7</v>
@@ -844,10 +793,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>7</v>
@@ -859,10 +808,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>7</v>
@@ -874,10 +823,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>7</v>
@@ -889,10 +838,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>7</v>
@@ -904,10 +853,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>7</v>
@@ -919,7 +868,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>37</v>
@@ -934,10 +883,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>38</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>39</v>
       </c>
       <c r="C17" t="s">
         <v>7</v>
@@ -948,10 +897,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>41</v>
       </c>
       <c r="C18" t="s">
         <v>7</v>
@@ -962,7 +911,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>42</v>
@@ -1004,10 +953,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C22" t="s">
         <v>7</v>
@@ -1018,10 +967,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C23" t="s">
         <v>7</v>
@@ -1032,10 +981,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C24" t="s">
         <v>7</v>
@@ -1046,10 +995,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C25" t="s">
         <v>7</v>
@@ -1060,10 +1009,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C26" t="s">
         <v>7</v>
@@ -1074,10 +1023,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C27" t="s">
         <v>7</v>
@@ -1088,10 +1037,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C28" t="s">
         <v>7</v>
@@ -1102,211 +1051,15 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C29" t="s">
         <v>7</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>55</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>55</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C31" t="s">
-        <v>7</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>58</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C32" t="s">
-        <v>7</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>58</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C33" t="s">
-        <v>7</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>61</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C34" t="s">
-        <v>7</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>61</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C35" t="s">
-        <v>7</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>11</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C36" t="s">
-        <v>7</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>65</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C37" t="s">
-        <v>7</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>67</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C38" t="s">
-        <v>7</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>12</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C39" t="s">
-        <v>7</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>70</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C40" t="s">
-        <v>7</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>70</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C41" t="s">
-        <v>7</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>73</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C42" t="s">
-        <v>7</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>75</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C43" t="s">
-        <v>7</v>
-      </c>
-      <c r="D43" s="5" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1323,31 +1076,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ECF9874-EDD0-4B43-8017-C343DACF060B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E44253C-7BBE-408C-B26C-F90E8214A3B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B4B167C-E39D-4259-B8BF-6C6368257CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="29">
   <si>
     <t>ERRO</t>
   </si>
@@ -71,88 +71,61 @@
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>lilian.sudati@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13568563600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>marcella.carraro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13570928600000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>gleison.ferreira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13551057100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>bruno.castro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13556524400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>caroline.wojciechowski@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13539013100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>luciana.belisario@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13565727500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>monica.prates@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13568192400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>itamar.junior@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13555376800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
     <t>adalberto.souza@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13562920800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>janaina.cazelato@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13551063400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>daniella.azevedo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13237451300000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>mauricio.santo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13277478600000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13496846000000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>carlos.neves@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12523663500000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12544900100000 Nota 242 - Retorno Cobrança</t>
+    <t>eliana.pedroso@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13560713200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>claudia.ribeiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13191704600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>eugenio.pereira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13567001300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>daniela.leal@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-5344751087 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>tatiana.monis@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13567773600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13569575000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>saulo.santiago@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13565198600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>diogo.junior@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13074613300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>raullison.castro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13107327200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13568915200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
   </si>
 </sst>
 </file>
@@ -608,10 +581,10 @@
     </row>
     <row r="3" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>9</v>
@@ -623,10 +596,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>9</v>
@@ -637,10 +610,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>9</v>
@@ -652,10 +625,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>9</v>
@@ -667,10 +640,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>9</v>
@@ -682,7 +655,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>21</v>
@@ -742,11 +715,11 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>29</v>
-      </c>
       <c r="C12" s="10" t="s">
         <v>9</v>
       </c>
@@ -756,78 +729,28 @@
       <c r="F12" s="6"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="C13" s="10"/>
+      <c r="D13" s="5"/>
       <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="C14" s="10"/>
+      <c r="D14" s="5"/>
       <c r="F14" s="6"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="C15" s="10"/>
+      <c r="D15" s="5"/>
       <c r="F15" s="3"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="5"/>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>6</v>
-      </c>
+    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C17" s="10"/>
+      <c r="D17" s="5"/>
       <c r="F17" s="3"/>
     </row>
   </sheetData>
@@ -843,31 +766,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ECF9874-EDD0-4B43-8017-C343DACF060B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA666F6F-75D2-4DA5-9CB0-BE8A6C1A42B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EC5DD5B-7B39-42B7-BAAC-F0AF6EF6C593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="97">
   <si>
     <t>ERRO</t>
   </si>
@@ -62,331 +62,274 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>jose.mergulhao@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-61573796000166 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
     <t>lilian.sudati@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13588658200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>edirilsa.bastos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13580698200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
     <t>juliano.guimaraes@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13498362200000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>daniela.leal@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12181415600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
     <t>bruno.rosa@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13576761400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13583373300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>sonia.bortoleto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13570474400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>juliana.diniz@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13580707900000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
     <t>gisele.cardoso1@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13575725200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>mayara.sampaio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13245367000000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>janaina.moura@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13580694200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>leandro.gonzaga@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13284948700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-14582466000157 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>eliane.fernandes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13587103200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>fernanda.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13577058700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>marcia.andreatti@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13582689600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>daniele.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13580636400000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>fernanda.carneiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13582063300000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13583821400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>monica.prates@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13551279300000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>nathalie.carmo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13580501400000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>claudia.malaggi@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13235716100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
     <t>rosana.teixeira@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13571096700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
     <t>gabriela.logrado@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13285490700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13555559200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13566745100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13576620100000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13587193200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13589891600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>lucas.monteiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13414321200000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>jonatas.lauretto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13580147100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13580188600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>carla.nascimento@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13412936300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>rodrigo.nascimento@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13530835500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>elaine.sousa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13584860100000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
     <t>david.silva2@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13586866000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>daniella.rodrigues@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13570665900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>wagner.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-47852612000176 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>daisy.marangoni@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13580438300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
     <t>claudenice.barbosa@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13580388200000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>filipe.pereira1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13584911700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-88820347600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-88821205100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>laerte.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13549650100000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>thomaz.jesus@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12448112600000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>renata.ferraz@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13289398300000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>silvia.plaza@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13296942500000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13311007100000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13311644000000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13325797300000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13328191400000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13337788500000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13346290700000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13396311800000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>barbara.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13494390100000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>ana.carneiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-61574273000134 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>janaina.reis@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-30292961804 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>jose.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12629853000000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>carlos.neves@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-2000038900000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11413117600000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12602695000000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12879647300000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12939412000000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>ana.brito@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13154400500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+    <t>Retorno de GO referência-13125579600000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13582175300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13591999000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>rodolfo.nantes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13532437900000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>isabel.cit@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13593318100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>eugenio.pereira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13567672100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>patricia.farias@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13597974700000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13264119600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>daiane.soares@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13583323600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>ana.sales@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13582337100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13590694300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>priscila.santana@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13585795500000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13569304100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>luciana.belisario@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13579424200000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>luciana.mayer@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13532134800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>danilo.ruas@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13593186600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>karen.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13593476400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>adriano.campos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13586860900000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>priscila.rubio@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13587804000000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13593504900000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>eduardo.marques@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13579488400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>marcia.castelo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13592996900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>daniela.gois@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13596415100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13587838900000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>rodrigo.amorim@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13590631200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13586597000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13593071600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13593591000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13593881000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>betina.carrasco@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13589378600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>leandro.susanj@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13583475600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>patricia.soares@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13582710900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>ivana.freitas@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13594339100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13579306800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13595902700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>lais.xavier@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13583409300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>rafael.leite@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13590220900004 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>enriete.saucedo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13566563400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13597976100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>rosemeire.faria@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13558609100000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13576121100000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13576131900000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13576201800000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13584039100000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13585308700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13585745200000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13587478400000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13588276700000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13595902700000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>danieli.ferreira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13572649100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>janaina.cazelato@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-3550307640 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>karina.vieira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12762122900000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13126600900000 Nota 167 - Retorno Cobrança</t>
   </si>
 </sst>
 </file>
@@ -827,13 +770,13 @@
     </row>
     <row r="2" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>6</v>
@@ -842,13 +785,13 @@
     </row>
     <row r="3" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>6</v>
@@ -857,13 +800,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>6</v>
@@ -871,13 +814,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>6</v>
@@ -886,13 +829,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>6</v>
@@ -901,13 +844,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>6</v>
@@ -916,13 +859,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>6</v>
@@ -931,13 +874,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>6</v>
@@ -946,13 +889,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>6</v>
@@ -961,13 +904,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>6</v>
@@ -976,13 +919,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>6</v>
@@ -991,13 +934,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>6</v>
@@ -1006,13 +949,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>6</v>
@@ -1021,13 +964,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>6</v>
@@ -1036,13 +979,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>6</v>
@@ -1051,13 +994,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>6</v>
@@ -1066,13 +1009,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>6</v>
@@ -1081,13 +1024,13 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>6</v>
@@ -1096,13 +1039,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>6</v>
@@ -1111,13 +1054,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>6</v>
@@ -1126,13 +1069,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>6</v>
@@ -1141,13 +1084,13 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C23" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>6</v>
@@ -1155,13 +1098,13 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>6</v>
@@ -1169,13 +1112,13 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C25" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>6</v>
@@ -1183,13 +1126,13 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C26" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>6</v>
@@ -1197,13 +1140,13 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C27" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>6</v>
@@ -1211,13 +1154,13 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C28" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>6</v>
@@ -1225,13 +1168,13 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>6</v>
@@ -1239,13 +1182,13 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C30" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>6</v>
@@ -1253,13 +1196,13 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C31" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>6</v>
@@ -1267,13 +1210,13 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>6</v>
@@ -1281,13 +1224,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C33" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>6</v>
@@ -1295,13 +1238,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C34" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>6</v>
@@ -1309,13 +1252,13 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C35" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>6</v>
@@ -1323,13 +1266,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C36" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>6</v>
@@ -1337,13 +1280,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C37" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>6</v>
@@ -1351,13 +1294,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C38" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>6</v>
@@ -1365,13 +1308,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C39" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>6</v>
@@ -1379,13 +1322,13 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C40" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>6</v>
@@ -1393,13 +1336,13 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>78</v>
       </c>
       <c r="C41" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>6</v>
@@ -1413,7 +1356,7 @@
         <v>80</v>
       </c>
       <c r="C42" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>6</v>
@@ -1421,13 +1364,13 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>79</v>
+      </c>
+      <c r="B43" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B43" s="6" t="s">
-        <v>82</v>
-      </c>
       <c r="C43" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>6</v>
@@ -1438,10 +1381,10 @@
         <v>79</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C44" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>6</v>
@@ -1452,10 +1395,10 @@
         <v>79</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C45" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>6</v>
@@ -1463,13 +1406,13 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>6</v>
@@ -1477,13 +1420,13 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>6</v>
@@ -1491,13 +1434,13 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>6</v>
@@ -1505,13 +1448,13 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C49" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>6</v>
@@ -1519,13 +1462,13 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C50" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>6</v>
@@ -1533,13 +1476,13 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B51" s="6" t="s">
-        <v>94</v>
-      </c>
       <c r="C51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>6</v>
@@ -1547,13 +1490,13 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>90</v>
+      </c>
+      <c r="B52" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B52" s="6" t="s">
-        <v>95</v>
-      </c>
       <c r="C52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>6</v>
@@ -1561,13 +1504,13 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C53" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>6</v>
@@ -1575,13 +1518,13 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C54" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>6</v>
@@ -1589,185 +1532,53 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C55" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>91</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C56" t="s">
-        <v>9</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D56" s="5"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>100</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C57" t="s">
-        <v>9</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D57" s="5"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>102</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C58" t="s">
-        <v>9</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D58" s="5"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>104</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C59" t="s">
-        <v>9</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D59" s="5"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>106</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C60" t="s">
-        <v>9</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D60" s="5"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>108</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C61" t="s">
-        <v>9</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D61" s="5"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>108</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C62" t="s">
-        <v>9</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D62" s="5"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>108</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C63" t="s">
-        <v>9</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D63" s="5"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>108</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C64" t="s">
-        <v>9</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>108</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C65" t="s">
-        <v>9</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>108</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C66" t="s">
-        <v>9</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>114</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C67" t="s">
-        <v>9</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D64" s="5"/>
+    </row>
+    <row r="65" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D65" s="5"/>
+    </row>
+    <row r="66" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D66" s="5"/>
+    </row>
+    <row r="67" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D67" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -1782,31 +1593,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ECF9874-EDD0-4B43-8017-C343DACF060B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{983D84D0-1A3D-49C8-9045-AC8A19389289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DA8EB77-8AD5-4691-89F6-5FB592C41FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="49">
   <si>
     <t>ERRO</t>
   </si>
@@ -62,67 +62,130 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>crislaine.trindade@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13501823200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>janaina.pazoto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13615242400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>jaciely.dias@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13401157000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>yuri.santos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13617761400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>renata.matheus@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13603087100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>leandro.machado@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13617803300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>mayara.sampaio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13607159200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>marco.schiabel@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13617588400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>leticia.bezerra@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13291921700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>joao.neto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13118073500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+    <t>mary.leme@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13619684100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>caroline.falcao@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13621162600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>valeria.palhares@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13619756700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>lucas.almeida@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13619163900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>andre.gouvea@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13619706000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>saulo.santiago@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13619685200000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>francieli.becker@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13618990900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>catia.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13612300000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13614114400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>erineuza.monzillo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13622284000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>bruno.ribas@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13615120500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>karen.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13611997100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>rosilene.nogueira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13619635400000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>eduardo.marques@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13502744300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>gilberto.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13619748100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>jonatas.lauretto@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13293169800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>lucas.monteiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13603992500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>rodrigo.nascimento@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13560014300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>jacqueline.mendes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13610116400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>david.silva2@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13197753100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>thays.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13611779200000 Nota 595 - ERRO PDF RETORNO</t>
   </si>
 </sst>
 </file>
@@ -531,7 +594,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.42578125" customWidth="1" collapsed="1"/>
@@ -563,13 +626,13 @@
     </row>
     <row r="2" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>6</v>
@@ -584,7 +647,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>6</v>
@@ -599,7 +662,7 @@
         <v>13</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>6</v>
@@ -613,7 +676,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>6</v>
@@ -628,7 +691,7 @@
         <v>17</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>6</v>
@@ -643,7 +706,7 @@
         <v>19</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>6</v>
@@ -658,7 +721,7 @@
         <v>21</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>6</v>
@@ -673,7 +736,7 @@
         <v>23</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>6</v>
@@ -682,13 +745,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="C10" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>6</v>
@@ -697,18 +760,172 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="C11" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" s="3"/>
+      <c r="B12" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -723,31 +940,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ECF9874-EDD0-4B43-8017-C343DACF060B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC3A0F53-CFBB-43F9-ADDF-BC0AC3D3C254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A2F818A-E1B9-4ADE-A5EC-5BCF3A5B8BB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="35">
   <si>
     <t>ERRO</t>
   </si>
@@ -62,109 +62,88 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>rodrigo.kuguyama@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13243215200000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>caroline.falcao@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13621406300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>ana.sales@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13575282900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>tatiana.monis@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13571479800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13622742800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>renata.magalhaes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13098767900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>eliane.fernandes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13617692500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>erineuza.monzillo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13459082200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>andrea.duarte@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13606964800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
     <t>gabriela.logrado@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13621129600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13621129600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13622523200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>leandro.susanj@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13370447500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13370508800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>rosemeire.faria@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13472712400000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>marli.rocha@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13606774500000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>laerte.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13584615200000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
     <t>thomaz.jesus@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12448112600000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>mauricio.santo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13458807200000 Nota 167 - Retorno Cobrança</t>
+    <t>ana.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13626719300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>thais.pessoto@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13616487700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13624909300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>sonia.bortoleto@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13164127100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>gisele.cardoso1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13622843800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>saulo.santiago@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13612908900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>fernanda.carneiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13609353500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13614381900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13619280900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13619342800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>bruna.carneiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13623396600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12448063500000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12762122900000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13126600900000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>paulo.baracy@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13493233000001 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>daniela.santos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-61574273000134 Nota 531 - Boleto Administrativo</t>
   </si>
 </sst>
 </file>
@@ -605,13 +584,13 @@
     </row>
     <row r="2" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>6</v>
@@ -620,13 +599,13 @@
     </row>
     <row r="3" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>6</v>
@@ -638,10 +617,10 @@
         <v>12</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>6</v>
@@ -649,13 +628,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>6</v>
@@ -664,13 +643,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>6</v>
@@ -679,13 +658,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>6</v>
@@ -694,13 +673,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>6</v>
@@ -709,13 +688,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>6</v>
@@ -724,13 +703,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>6</v>
@@ -739,13 +718,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>26</v>
-      </c>
       <c r="C11" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>6</v>
@@ -754,13 +733,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>6</v>
@@ -769,13 +748,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>6</v>
@@ -784,13 +763,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>30</v>
-      </c>
       <c r="C14" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>6</v>
@@ -799,13 +778,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>6</v>
@@ -814,13 +793,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>33</v>
-      </c>
       <c r="C16" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>6</v>
@@ -829,13 +808,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>35</v>
-      </c>
       <c r="C17" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>6</v>
@@ -843,48 +822,18 @@
       <c r="F17" s="3"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="C18" s="10"/>
+      <c r="D18" s="5"/>
       <c r="F18" s="6"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="C19" s="10"/>
+      <c r="D19" s="5"/>
       <c r="F19" s="3"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="C20" s="10"/>
+      <c r="D20" s="5"/>
       <c r="F20" s="6"/>
     </row>
   </sheetData>
@@ -900,31 +849,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ECF9874-EDD0-4B43-8017-C343DACF060B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAD1EA56-4364-4ECC-814E-7AC3269C91E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EC56324-6ED2-4D10-9DFB-96E8FFB61851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="62">
   <si>
     <t>ERRO</t>
   </si>
@@ -62,262 +62,169 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>lilian.sudati@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12869244000000 Nota 595 - ERRO PDF retorno</t>
+    <t>lucas.pereira1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13556937300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
   </si>
   <si>
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13369486300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>daniel.lourenco@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13597536100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>caroline.falcao@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13460152300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>edirilsa.bastos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13626075800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13628828000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>eugenio.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13616204400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>bruno.rosa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13279069500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>daiane.soares@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13612715400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>wilson.filho@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13627764700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>sara.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13633812100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>sonia.bortoleto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13613964500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>caroline.wojciechowski@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13622599800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13625213900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>luiz.santos1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13620017500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>mayara.sampaio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13303702800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>danilo.ruas@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13626653200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>luiza.brandao@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13624814200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>clarissa.cavalli@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13287560500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>jorge.zimke@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13616970100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>bruna.teixeira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13633268300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>fabiane.alessi@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13613649000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13625711700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>veruscka.reis@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13179161700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>pamela.burige@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13558473700000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>claudia.malaggi@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13622052000000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>eduardo.marques@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13624262600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>deise.santos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13422338800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>daniele.beck@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13633607600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>aline.vieira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13623626500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>dayane.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13628274600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+    <t>jessica.gimenes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13614172300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>jefferson.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13625338000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>jaciely.dias@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13627320400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>patricia.farias@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13628967900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>rudnelio.luz@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13629477900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>lucas.almeida@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13625881800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>luana.marton1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13383465400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13624799900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>priscila.sousa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13634326100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>priscila.santana@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13169837700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>gisele.cardoso1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13636021200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>erica.cassandre@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13177197900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>ketlin.vega@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13634387900000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>bernardo.barbosa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13626267800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>andre.gouvea@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13627049500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>marcos.machado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13624604000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>endyane.marques@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13625846200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>gustavo.arruda@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13626511200000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
   </si>
   <si>
     <t>gabriela.logrado@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13628836400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13629263900000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13630829000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13630885300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13631609700000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13631654100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13631879800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13631966500000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>rafael.leite@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13383300700000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>ana.rodrigues@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13511801900000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>ilcileia.guimaraes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13618061300000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>marcos.penachioni@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13540511800000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>marcia.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-61574273000134 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>andrea.barros@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13606415500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>carlos.neves@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12957673000000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13022336000000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13224015000000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>matheus.ferreira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13107165700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+    <t>Retorno de GO referência-13633190600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13633881700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13634310400000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13635434500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>jonatas.lauretto@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13293169800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>daniella.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13635125200000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>hugo.costa1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13630393200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>edson.jesus@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13286959800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>rose.lourenco@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13613286300000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>maria.ferro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13633339000000 Nota 595 - ERRO PDF retorno</t>
   </si>
 </sst>
 </file>
@@ -726,7 +633,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.42578125" customWidth="1" collapsed="1"/>
@@ -773,10 +680,10 @@
     </row>
     <row r="3" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>9</v>
@@ -788,10 +695,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>9</v>
@@ -802,10 +709,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>9</v>
@@ -817,10 +724,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>9</v>
@@ -832,10 +739,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>9</v>
@@ -847,10 +754,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>9</v>
@@ -862,10 +769,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>9</v>
@@ -880,7 +787,7 @@
         <v>22</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>9</v>
@@ -892,10 +799,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>9</v>
@@ -907,10 +814,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>9</v>
@@ -922,10 +829,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>9</v>
@@ -937,10 +844,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>9</v>
@@ -952,10 +859,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>9</v>
@@ -967,10 +874,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>9</v>
@@ -982,10 +889,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>9</v>
@@ -997,10 +904,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>9</v>
@@ -1012,10 +919,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>9</v>
@@ -1027,10 +934,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>9</v>
@@ -1042,10 +949,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>9</v>
@@ -1060,7 +967,7 @@
         <v>45</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>9</v>
@@ -1072,7 +979,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>48</v>
@@ -1086,7 +993,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>49</v>
@@ -1179,286 +1086,6 @@
         <v>9</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>62</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C31" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>64</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C32" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>66</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C33" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>66</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C34" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>66</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C35" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>66</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C36" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>66</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>66</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C38" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>66</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C39" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>66</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C40" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>75</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C41" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>77</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C42" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>79</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C43" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>81</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C44" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>83</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C45" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>85</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C46" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>87</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C47" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>87</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C48" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>87</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C49" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>91</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C50" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" s="5" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1475,31 +1102,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ECF9874-EDD0-4B43-8017-C343DACF060B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ECF9874-EDD0-4B43-8017-C343DACF060B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94077294-E61F-400E-ACC3-2B6BE4631CE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B7C1F3B-BDF8-455A-A990-E169AD596387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="95">
   <si>
     <t>ERRO</t>
   </si>
@@ -62,379 +62,268 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>lilian.sudati@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13641645600000 Nota 595 - ERRO PDF</t>
+    <t>denise.nogueira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-49906914000105 Nota 242 - Retorno Cobrança</t>
   </si>
   <si>
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>camila.almeida@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13640238400000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>renato.lopes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13643399700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>william.rosa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13611616700000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>edirilsa.bastos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13626738200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>mariana.dolence@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13644938700000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>rodrigo.santos1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13640443200000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13640486400000 Nota 595 - ERRO PDF</t>
+    <t>joao.carvalho2@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13638682400000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>juliano.guimaraes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13643979600000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>rosthiane.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13520720000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
   </si>
   <si>
     <t>renata.magalhaes@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-11340234300000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13634277700000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>bruna.carneiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13641759300000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>daniel.iarrocheski@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13568968200000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>bruno.rosa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13568966500000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>ana.sales@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13643843900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>elisa.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13136142800000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>priscila.sousa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13629232800000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>jose.junior3@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13635688000000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13098767900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>rodrigo.kuguyama@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13611851500000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>caroline.batalha@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13540584500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13638178000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>karina.barros@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13642700700000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>ana.margarida@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13632883900000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
   </si>
   <si>
     <t>sonia.bortoleto@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13643447600000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13645339200000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>gisele.cardoso1@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13407572300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13625239300000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>ketlin.vega@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13600389300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>mayara.sampaio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13634073500000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>tullio.yoshinaga@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13633545000000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>andriele.pala@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13640050700000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13640051000000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13641346100000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>ana.arruda@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13636636400000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13641903800000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>francieli.becker@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13431238400021 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>luiza.brandao@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13637873800000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13640108000000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>rubiane.bendlin@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13641358900000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>kely.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13623007600000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>grasiela.dias@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13639832600000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>olga.terceiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13640576600000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13639477800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>carla.ventura@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13644798600000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>luciana.mayer@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13633684900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>patricia.vieira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13641235900000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>eliane.fernandes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13645902000000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>saulo.santiago@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13632556600000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>daniele.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13642349200000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>douglas.pereira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13598760600000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>viviane.corbari@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13625079400000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13635216700000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>veruscka.reis@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13641040400000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>monica.prates@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13641751600000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>daniela.gois@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13638211200000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>eduardo.rovina@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13645230500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>eduardo.marques@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13645356800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>rodrigo.amorim@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13640515300000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13564827500000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>carolline.acioly@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13588147700000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13588172800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13588301500000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13588322900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>andrea.duarte@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13644915500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>daniele.beck@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13638434400000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>dayane.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13603934300000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>aline.vieira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13624318500000 Nota 7022 - Help Desk</t>
   </si>
   <si>
     <t>raullison.castro@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13620166400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13624432000000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13628852900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13629862100000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13642050500000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13628852900000 Nota 7022 - Help Desk</t>
   </si>
   <si>
     <t>gabriela.logrado@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13634617000000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>francismary.barros@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13639648500000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13644041500000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>geiza.vinand@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13635670300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>aline.madeira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13641084800000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>betina.carrasco@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13642462300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13642507100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>matheus.dias@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13635268800000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>rodrigo.nascimento@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13643700900000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>julianna.printes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13636830200000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>rosilene.nogueira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13640154500000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>sofia.magalhaes1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13633399400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>david.silva2@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13336193400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13640359900000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>thays.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13636537900000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>lais.xavier@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13641648400000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>ana.salomao@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13637085300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>leinny.amorim@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13634038000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>laila.steil@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13633704200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>cassia.silveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13634577800000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>ilcileia.guimaraes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13628435400000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13629639900000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13634885900000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13636184800000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>ana.rodrigues@allianz.com.br</t>
+    <t>Retorno de GO referência-13636495300000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13641635000000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>graziela.salvioni@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13643265100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>lucas.monteiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13640105400000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>jonatas.lauretto@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13640393400000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13640568500000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>marcelly.vericimo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13589837400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>itamar.junior@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13631933700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>fabio.ribeiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13636758900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13642427800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>elaine.sousa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13404861300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>daisy.marangoni@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13610013400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>marcia.pereira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13105394100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>daniele.borges@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-26610546000158 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>carlos.neves@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12618328400000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12866353800000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12957673000000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13143867500000 Nota 242 - Retorno Cobrança</t>
   </si>
 </sst>
 </file>
@@ -843,7 +732,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.42578125" customWidth="1" collapsed="1"/>
@@ -1009,10 +898,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>9</v>
@@ -1024,10 +913,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>9</v>
@@ -1039,10 +928,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>9</v>
@@ -1054,10 +943,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>9</v>
@@ -1069,10 +958,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>9</v>
@@ -1084,10 +973,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>9</v>
@@ -1099,10 +988,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>9</v>
@@ -1114,10 +1003,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>9</v>
@@ -1129,10 +1018,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>9</v>
@@ -1144,10 +1033,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>9</v>
@@ -1159,10 +1048,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>9</v>
@@ -1177,7 +1066,7 @@
         <v>45</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>9</v>
@@ -1189,10 +1078,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C23" t="s">
         <v>9</v>
@@ -1203,10 +1092,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C24" t="s">
         <v>9</v>
@@ -1217,7 +1106,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>52</v>
@@ -1231,7 +1120,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>53</v>
@@ -1245,7 +1134,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>54</v>
@@ -1273,10 +1162,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C29" t="s">
         <v>9</v>
@@ -1287,10 +1176,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C30" t="s">
         <v>9</v>
@@ -1301,10 +1190,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C31" t="s">
         <v>9</v>
@@ -1315,10 +1204,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C32" t="s">
         <v>9</v>
@@ -1329,10 +1218,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C33" t="s">
         <v>9</v>
@@ -1346,7 +1235,7 @@
         <v>65</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C34" t="s">
         <v>9</v>
@@ -1357,10 +1246,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C35" t="s">
         <v>9</v>
@@ -1371,10 +1260,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C36" t="s">
         <v>9</v>
@@ -1385,10 +1274,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C37" t="s">
         <v>9</v>
@@ -1399,7 +1288,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>74</v>
@@ -1455,10 +1344,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>79</v>
+      </c>
+      <c r="B42" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>82</v>
       </c>
       <c r="C42" t="s">
         <v>9</v>
@@ -1469,10 +1358,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" s="6" t="s">
         <v>83</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>84</v>
       </c>
       <c r="C43" t="s">
         <v>9</v>
@@ -1483,7 +1372,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>85</v>
@@ -1497,10 +1386,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C45" t="s">
         <v>9</v>
@@ -1511,10 +1400,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C46" t="s">
         <v>9</v>
@@ -1525,10 +1414,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C47" t="s">
         <v>9</v>
@@ -1539,10 +1428,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C48" t="s">
         <v>9</v>
@@ -1553,10 +1442,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C49" t="s">
         <v>9</v>
@@ -1567,323 +1456,15 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C50" t="s">
         <v>9</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>94</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C51" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>96</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C52" t="s">
-        <v>9</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>98</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C53" t="s">
-        <v>9</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>98</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C54" t="s">
-        <v>9</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>101</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C55" t="s">
-        <v>9</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>103</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C56" t="s">
-        <v>9</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>105</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C57" t="s">
-        <v>9</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>107</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C58" t="s">
-        <v>9</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>109</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C59" t="s">
-        <v>9</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>111</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C60" t="s">
-        <v>9</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>111</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C61" t="s">
-        <v>9</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>114</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C62" t="s">
-        <v>9</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>116</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C63" t="s">
-        <v>9</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>118</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="C64" t="s">
-        <v>9</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>120</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C65" t="s">
-        <v>9</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>122</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C66" t="s">
-        <v>9</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>124</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C67" t="s">
-        <v>9</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>126</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C68" t="s">
-        <v>9</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>126</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C69" t="s">
-        <v>9</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>126</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="C70" t="s">
-        <v>9</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>126</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="C71" t="s">
-        <v>9</v>
-      </c>
-      <c r="D71" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>131</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C72" t="s">
-        <v>9</v>
-      </c>
-      <c r="D72" s="5" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B7C1F3B-BDF8-455A-A990-E169AD596387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF566176-4E5C-4E77-A8DA-D732BF00D656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RetornoGo" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="98">
   <si>
     <t>ERRO</t>
   </si>
@@ -62,268 +62,277 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>denise.nogueira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-49906914000105 Nota 242 - Retorno Cobrança</t>
+    <t>inara.couto@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13638668400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
   </si>
   <si>
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>joao.carvalho2@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13638682400000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>juliano.guimaraes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13643979600000 Nota 595 - ERRO PDF</t>
+    <t>eliana.pedroso@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13645952000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>mary.leme@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13648482100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>matheus.gomes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13648949400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>diego.vasconcelos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13634753700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>evaldo.cardoso@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13646288800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13646312200000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>kaue.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13315418300000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>raquel.sech@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13430992100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13611906400000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>caroline.falcao@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13638623500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>valeria.palhares@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13429178900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
   </si>
   <si>
     <t>rosthiane.oliveira@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13520720000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>renata.magalhaes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13098767900000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>rodrigo.kuguyama@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13611851500000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>caroline.batalha@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13540584500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13638178000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>karina.barros@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13642700700000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>ana.margarida@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13632883900000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>sonia.bortoleto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13645339200000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>gisele.cardoso1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13639477800000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13647079100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>juliana.almeida@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13648902600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>wilson.filho@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13581889100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>vanessa.campos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13632471300000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13642634500000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>elisa.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13261983100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>tiago.nascimento@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13639008000000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
   </si>
   <si>
     <t>carla.ventura@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13644798600000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>luciana.mayer@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13633684900000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>patricia.vieira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13641235900000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>eliane.fernandes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13645902000000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>saulo.santiago@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13632556600000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>daniele.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13642349200000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>douglas.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13598760600000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>viviane.corbari@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13625079400000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13635216700000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13640146700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>ketlin.vega@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13646310100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>viviane.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13647306300000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>clarissa.cavalli@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13523989400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>jorge.zimke@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13630435700000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>veruscka.reis@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13564827500000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13644293200000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>carolline.acioly@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13588147700000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13588172800000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13588301500000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13588322900000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>andrea.duarte@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13644915500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>daniele.beck@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13638434400000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>dayane.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13603934300000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>aline.vieira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13624318500000 Nota 7022 - Help Desk</t>
-  </si>
-  <si>
-    <t>raullison.castro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13628852900000 Nota 7022 - Help Desk</t>
+    <t>Retorno de GO referência-13538326800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>claudia.malaggi@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13626629900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>rodrigo.amorim@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13646760800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13648366300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
   </si>
   <si>
     <t>gabriela.logrado@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13636495300000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13641635000000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>graziela.salvioni@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13643265100000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13172586800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13638185800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13639892800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13639948600000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13640626800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13642151400000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13643584600000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13643745800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13645229700000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13645292600000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13645501400000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13646789800000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>lucas.monteiro@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13640105400000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>jonatas.lauretto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13640393400000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13640568500000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>marcelly.vericimo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13589837400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>itamar.junior@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13631933700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>fabio.ribeiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13636758900000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13642427800000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>elaine.sousa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13404861300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>daisy.marangoni@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13610013400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>marcia.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13105394100000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>daniele.borges@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-26610546000158 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>carlos.neves@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12618328400000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12866353800000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12957673000000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13143867500000 Nota 242 - Retorno Cobrança</t>
+    <t>Retorno de GO referência-13646473400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>rafaela.jeronimo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13645201000000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>jheniffer.emiliano@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13647478800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>sofia.magalhaes1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13417459300000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>aparecida.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13648319200000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>rafael.leite@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13288608900000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>leinny.amorim@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13643960500000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>cassia.silveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13645192900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>lucidene.santana@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13401003600000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>rosemeire.faria@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13411425900000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13620370100000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13638683000000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>ana.rodrigues@allianz.com.br</t>
   </si>
 </sst>
 </file>
@@ -732,7 +741,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.42578125" customWidth="1" collapsed="1"/>
@@ -853,10 +862,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>21</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>9</v>
@@ -868,7 +877,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>22</v>
@@ -898,10 +907,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>26</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>9</v>
@@ -913,10 +922,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>27</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>28</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>9</v>
@@ -928,10 +937,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>9</v>
@@ -943,10 +952,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>32</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>9</v>
@@ -958,10 +967,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>33</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>34</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>9</v>
@@ -973,10 +982,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>35</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>36</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>9</v>
@@ -988,10 +997,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>9</v>
@@ -1003,10 +1012,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>9</v>
@@ -1018,10 +1027,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>9</v>
@@ -1033,10 +1042,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>9</v>
@@ -1048,10 +1057,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>9</v>
@@ -1066,7 +1075,7 @@
         <v>45</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>9</v>
@@ -1078,10 +1087,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>48</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>49</v>
       </c>
       <c r="C23" t="s">
         <v>9</v>
@@ -1092,10 +1101,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>50</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>51</v>
       </c>
       <c r="C24" t="s">
         <v>9</v>
@@ -1106,7 +1115,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>52</v>
@@ -1120,10 +1129,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C26" t="s">
         <v>9</v>
@@ -1134,10 +1143,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C27" t="s">
         <v>9</v>
@@ -1148,10 +1157,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C28" t="s">
         <v>9</v>
@@ -1162,10 +1171,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C29" t="s">
         <v>9</v>
@@ -1179,7 +1188,7 @@
         <v>59</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C30" t="s">
         <v>9</v>
@@ -1190,10 +1199,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C31" t="s">
         <v>9</v>
@@ -1204,7 +1213,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>64</v>
@@ -1218,10 +1227,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" s="6" t="s">
         <v>65</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>66</v>
       </c>
       <c r="C33" t="s">
         <v>9</v>
@@ -1232,10 +1241,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C34" t="s">
         <v>9</v>
@@ -1246,10 +1255,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C35" t="s">
         <v>9</v>
@@ -1260,10 +1269,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C36" t="s">
         <v>9</v>
@@ -1274,10 +1283,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C37" t="s">
         <v>9</v>
@@ -1288,10 +1297,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C38" t="s">
         <v>9</v>
@@ -1302,10 +1311,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C39" t="s">
         <v>9</v>
@@ -1316,10 +1325,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C40" t="s">
         <v>9</v>
@@ -1330,10 +1339,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C41" t="s">
         <v>9</v>
@@ -1344,10 +1353,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C42" t="s">
         <v>9</v>
@@ -1358,10 +1367,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C43" t="s">
         <v>9</v>
@@ -1372,10 +1381,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C44" t="s">
         <v>9</v>
@@ -1386,10 +1395,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C45" t="s">
         <v>9</v>
@@ -1400,10 +1409,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C46" t="s">
         <v>9</v>
@@ -1414,10 +1423,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C47" t="s">
         <v>9</v>
@@ -1428,10 +1437,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C48" t="s">
         <v>9</v>
@@ -1442,10 +1451,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C49" t="s">
         <v>9</v>
@@ -1456,15 +1465,113 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>89</v>
+      </c>
+      <c r="B50" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="C50" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>89</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C51" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>91</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C52" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>93</v>
+      </c>
+      <c r="B53" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="C50" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" s="5" t="s">
+      <c r="C53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>91</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>91</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C55" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>97</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C56" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>97</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C57" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="5" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5A3A31-30C8-4443-A713-B28871137274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2699916A-A93E-443C-A09C-0941B904C67A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="178">
   <si>
     <t>ERRO</t>
   </si>
@@ -62,121 +62,136 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>crislaine.trindade@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13545990000000 Nota 595 - ERRO PDF</t>
+    <t>diogo.junior@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13655036100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
   </si>
   <si>
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
+    <t>mary.leme@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13401445700000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
     <t>lilian.sudati@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13584402700000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>juliano.guimaraes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13259520800000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13436660800000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>mariana.perez1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13576876000000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>matheus.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13638414400000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13647142300000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13648976700000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13649908200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>luiz.junior@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13647754900000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>jaciely.dias@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13250548900000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13516120500000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>nilcea.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13646025300000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13648197400000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13435276400000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13656342700000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>ana.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13648860400000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>joao.fernandes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13653108200000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>rosthiane.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13637344600000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>rodrigo.santos1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13647471400000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>renata.magalhaes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11340234300000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>bruna.carneiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13644671800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13650317300000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>eugenio.pereira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13656132300000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>patricia.farias@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13650260300000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>vanessa.campos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13332083500000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13425494400000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13657166300000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>daiane.soares@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13648230700000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>joelson.farias@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13559512700000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>lucas.almeida@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13205199600000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13625881800000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>gleison.ferreira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13647805500000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13650819400000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>elisangela.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13492996500000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13637903800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>ana.margarida@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13651170300000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13652338600000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>kaue.medeiros@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13568996500000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>alessiane.carvalho@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13642427700000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>luana.marton1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13651962700000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>jose.junior3@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13656182100000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>renata.matheus@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13643242700000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13651261400000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13149023600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
   </si>
   <si>
     <t>tiago.nascimento@allianz.com.br</t>
@@ -188,319 +203,319 @@
     <t>Retorno de GO referência-10163804300000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
+    <t>gisele.cardoso1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13447774300000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13643528500000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
     <t>andreia.brixner@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13640878700000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>gisele.cardoso1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13648421700000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13648520200000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>caroline.wojciechowski@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13648575600000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>carla.ventura@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13651867500000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>tatiana.monis@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13569106400000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>erica.cassandre@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13642979400000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13651645300000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>ketlin.vega@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13650297800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>leandro.machado@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13639671600000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>douglas.morais@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13646654200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>bernardo.barbosa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13649811400000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13650187800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>raphael.callado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13655111800000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>claudia.gomes@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13651965700000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>mayara.sampaio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13600676600000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>andriele.pala@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13645602500000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13644017900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>viviane.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13650891100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>luciana.belisario@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13651212800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>luciana.mayer@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13651737700000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>patricia.vieira@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13648914900000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>luciana.mayer@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13650119700000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>eliane.fernandes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13651301700000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13653915100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>saulo.santiago@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13624067000000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13639510800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>danilo.ruas@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13645253800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>andreza.libanore@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13645457300000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>fernanda.silva@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13411267200000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13243288900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>marcia.andreatti@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13478970100000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>luiza.brandao@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13650855500000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13651941300000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>jorge.zimke@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11816365700000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11816438900000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13529222000000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13652489400000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>catia.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13650160300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
   </si>
   <si>
     <t>viviane.corbari@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13638485000000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13530272400000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13629378400000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>bruno.ribas@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13292301300000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13644218400000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13649908600000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>karen.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13648746800000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13650885900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13653514500000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>kely.silva@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13649932000000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>beatriz.santos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13212975200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+    <t>Retorno de GO referência-13647859300000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>aline.carpes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13650115800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>andreia.cardias@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13651788600000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>olga.terceiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13648045400000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>veruscka.reis@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13648578900000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>olga.terceiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13651365200000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13653748800000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>raphael.silva@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13639015800000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>marcos.machado@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13648588500000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13651257900000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13649902500000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>adriano.campos@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13348624000000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>andrea.duarte@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13529902700000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>daniele.beck@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13646444100000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>gabriela.logrado@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13642144300000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>francismary.barros@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13643652700000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13642328500000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>carolline.acioly@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13650055000000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>claudia.malaggi@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13277727700012 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13617632800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13656619500000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>cassia.souza@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13644804400000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>raullison.castro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13641244000000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13641530000000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13641557100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13641593600000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13641625900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13641662500000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13641676100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13641953600000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13641958000000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>lucas.monteiro@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13648044100000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>jonatas.lauretto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13653118900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>cristiane.konrad@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13645122000000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13649895300000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>marcelly.vericimo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13177784100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>iury.fuly@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13650432000000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13650666600000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>rodrigo.nascimento@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13558932200000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13650711400000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>jacqueline.mendes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13582298100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>rafaela.jeronimo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13653282500000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>patricia.soares@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13301872200000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>ivana.freitas@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13569103100000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13648403100000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13648604100000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>larissa.araujo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13651594300000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>jheniffer.emiliano@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13462903100000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>christian.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13647969300000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13653668700000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>endyane.marques@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13648916300000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13654315800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>marcio.ferreira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13647075600000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13412054800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>julianna.printes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13646124300000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>rosilene.nogueira@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13650750900000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13650994800000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13646463600000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13652984500000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13655828600000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>andrea.farias1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13644404700000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>david.silva2@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13641720500000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13650741400000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13651278400000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>lais.xavier@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13177027900000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13648653200000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13651753600000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>rafael.leite@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13569007400000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>daniella.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13651733700000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>thays.silva@allianz.com.br</t>
@@ -509,52 +524,55 @@
     <t>Retorno de GO referência-13653574300000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
-    <t>diego.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12014698500434 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13647738500000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>sabrina.azevedo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13649831200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+    <t>ana.salomao@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13657258800000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>leinny.amorim@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13649921400000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>eduardo.santos1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13646073000000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>ivone.jesus@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13505709700000 Nota 167 - Retorno Cobrança</t>
+    <t>Retorno de GO referência-13651778500000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>aires.junior@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13654219500000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>enriete.saucedo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13645863100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>alan.peter@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13646817200000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>laila.steil@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13656657600000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>carolina.lima@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13641465600000 Nota 472 - Reentrada OK Produto</t>
+    <t>Retorno de GO referência-13414422800000 Nota 472 - Reentrada OK Produto</t>
   </si>
   <si>
     <t>ana.rodrigues@allianz.com.br</t>
   </si>
   <si>
-    <t>thomaz.jesus@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13447980800000 Nota 167 - Retorno Cobrança</t>
+    <t>fabiana.aquino@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13657068100000 Nota 595 - ERRO PDF</t>
   </si>
 </sst>
 </file>
@@ -963,7 +981,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:F98"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.42578125" customWidth="1" collapsed="1"/>
@@ -1039,7 +1057,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>14</v>
@@ -1084,10 +1102,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>9</v>
@@ -1099,10 +1117,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>9</v>
@@ -1114,10 +1132,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>9</v>
@@ -1129,10 +1147,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>9</v>
@@ -1144,10 +1162,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>9</v>
@@ -1159,10 +1177,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>9</v>
@@ -1174,10 +1192,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>9</v>
@@ -1189,10 +1207,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>9</v>
@@ -1204,10 +1222,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>9</v>
@@ -1219,10 +1237,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>9</v>
@@ -1234,10 +1252,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>9</v>
@@ -1249,10 +1267,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>9</v>
@@ -1264,10 +1282,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>9</v>
@@ -1279,10 +1297,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>9</v>
@@ -1294,10 +1312,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>9</v>
@@ -1309,10 +1327,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C23" t="s">
         <v>9</v>
@@ -1323,10 +1341,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C24" t="s">
         <v>9</v>
@@ -1337,10 +1355,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C25" t="s">
         <v>9</v>
@@ -1351,10 +1369,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C26" t="s">
         <v>9</v>
@@ -1365,10 +1383,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C27" t="s">
         <v>9</v>
@@ -1379,10 +1397,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C28" t="s">
         <v>9</v>
@@ -1393,10 +1411,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C29" t="s">
         <v>9</v>
@@ -1407,10 +1425,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C30" t="s">
         <v>9</v>
@@ -1421,10 +1439,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C31" t="s">
         <v>9</v>
@@ -1435,10 +1453,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C32" t="s">
         <v>9</v>
@@ -1449,10 +1467,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C33" t="s">
         <v>9</v>
@@ -1463,10 +1481,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C34" t="s">
         <v>9</v>
@@ -1477,10 +1495,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C35" t="s">
         <v>9</v>
@@ -1491,10 +1509,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C36" t="s">
         <v>9</v>
@@ -1505,10 +1523,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C37" t="s">
         <v>9</v>
@@ -1519,10 +1537,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C38" t="s">
         <v>9</v>
@@ -1533,10 +1551,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C39" t="s">
         <v>9</v>
@@ -1547,10 +1565,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C40" t="s">
         <v>9</v>
@@ -1561,10 +1579,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C41" t="s">
         <v>9</v>
@@ -1575,10 +1593,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C42" t="s">
         <v>9</v>
@@ -1589,10 +1607,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C43" t="s">
         <v>9</v>
@@ -1603,10 +1621,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C44" t="s">
         <v>9</v>
@@ -1617,10 +1635,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C45" t="s">
         <v>9</v>
@@ -1631,10 +1649,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C46" t="s">
         <v>9</v>
@@ -1645,10 +1663,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C47" t="s">
         <v>9</v>
@@ -1659,10 +1677,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C48" t="s">
         <v>9</v>
@@ -1673,10 +1691,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C49" t="s">
         <v>9</v>
@@ -1687,10 +1705,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C50" t="s">
         <v>9</v>
@@ -1701,10 +1719,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C51" t="s">
         <v>9</v>
@@ -1715,10 +1733,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="C52" t="s">
         <v>9</v>
@@ -1729,10 +1747,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C53" t="s">
         <v>9</v>
@@ -1743,10 +1761,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C54" t="s">
         <v>9</v>
@@ -1757,10 +1775,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C55" t="s">
         <v>9</v>
@@ -1771,10 +1789,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C56" t="s">
         <v>9</v>
@@ -1785,10 +1803,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="C57" t="s">
         <v>9</v>
@@ -1799,10 +1817,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C58" t="s">
         <v>9</v>
@@ -1813,10 +1831,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="C59" t="s">
         <v>9</v>
@@ -1827,10 +1845,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C60" t="s">
         <v>9</v>
@@ -1841,10 +1859,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C61" t="s">
         <v>9</v>
@@ -1855,10 +1873,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C62" t="s">
         <v>9</v>
@@ -1869,10 +1887,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C63" t="s">
         <v>9</v>
@@ -1883,10 +1901,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C64" t="s">
         <v>9</v>
@@ -1900,7 +1918,7 @@
         <v>116</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C65" t="s">
         <v>9</v>
@@ -1911,10 +1929,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C66" t="s">
         <v>9</v>
@@ -1925,10 +1943,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C67" t="s">
         <v>9</v>
@@ -1939,10 +1957,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C68" t="s">
         <v>9</v>
@@ -1953,7 +1971,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>125</v>
@@ -2009,7 +2027,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>132</v>
@@ -2023,10 +2041,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C74" t="s">
         <v>9</v>
@@ -2037,7 +2055,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>135</v>
@@ -2093,10 +2111,10 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C79" t="s">
         <v>9</v>
@@ -2107,10 +2125,10 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C80" t="s">
         <v>9</v>
@@ -2121,10 +2139,10 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C81" t="s">
         <v>9</v>
@@ -2135,10 +2153,10 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C82" t="s">
         <v>9</v>
@@ -2149,7 +2167,7 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>149</v>
@@ -2163,10 +2181,10 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C84" t="s">
         <v>9</v>
@@ -2177,10 +2195,10 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C85" t="s">
         <v>9</v>
@@ -2194,7 +2212,7 @@
         <v>152</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C86" t="s">
         <v>9</v>
@@ -2205,10 +2223,10 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C87" t="s">
         <v>9</v>
@@ -2219,10 +2237,10 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C88" t="s">
         <v>9</v>
@@ -2233,10 +2251,10 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C89" t="s">
         <v>9</v>
@@ -2247,10 +2265,10 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C90" t="s">
         <v>9</v>
@@ -2261,10 +2279,10 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C91" t="s">
         <v>9</v>
@@ -2275,10 +2293,10 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C92" t="s">
         <v>9</v>
@@ -2289,10 +2307,10 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C93" t="s">
         <v>9</v>
@@ -2303,10 +2321,10 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C94" t="s">
         <v>9</v>
@@ -2317,10 +2335,10 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="C95" t="s">
         <v>9</v>
@@ -2331,10 +2349,10 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>127</v>
+        <v>174</v>
       </c>
       <c r="C96" t="s">
         <v>9</v>
@@ -2345,10 +2363,10 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C97" t="s">
         <v>9</v>
@@ -2359,29 +2377,15 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="C98" t="s">
         <v>9</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>170</v>
-      </c>
-      <c r="B99" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="C99" t="s">
-        <v>9</v>
-      </c>
-      <c r="D99" s="5" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2699916A-A93E-443C-A09C-0941B904C67A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F595A1-A609-42C1-A39D-1BB8DCE117D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="268">
   <si>
     <t>ERRO</t>
   </si>
@@ -62,517 +62,787 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>diogo.junior@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13655036100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+    <t>thiago.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13655015800000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>mary.leme@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13401445700000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>lilian.sudati@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13435276400000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13656342700000 Nota 595 - ERRO PDF</t>
+    <t>nathalie.carmo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13646928200000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>ana.oliveira@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13648860400000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>joao.fernandes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13653108200000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>rosthiane.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13637344600000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>rodrigo.santos1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13647471400000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>renata.magalhaes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11340234300000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13649365400000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>camila.almeida@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13651229500000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>evaldo.cardoso@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13651470800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13653679700000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13654582300000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13656205100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>diego.vasconcelos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13656262800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13658726100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>kaue.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13648411100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13651366800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13651388800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>joao.carvalho2@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13652958500000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>luiz.inocente@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13657270300000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>fernanda.goncalves1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13650836500000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>valeria.palhares@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13649455900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>izabela.cuba@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13624729000000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13652051800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13654707900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>mariana.perez1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13570679500000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13654755900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>juliano.guimaraes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13655003500000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>fabio.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13645505200000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>fernando.duque@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13648337200000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13651475300000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13651571500000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13651723900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13652354000000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13653216300000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>bruna.carneiro@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13644671800000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13650317300000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13652188900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13657226200000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>nilcea.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13424472700000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>claudia.ribeiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13654297600000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>eugenio.pereira@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13656132300000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13658644400000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>patricia.farias@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13657166300000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>daiane.soares@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13648230700000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>joelson.farias@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13559512700000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13656794400000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>bruno.rosa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13170785200000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13653517700000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>sara.pereira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13568964900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13626124300000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13626163400000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13652723400000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>jessica.silva3@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13642100100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>ana.margarida@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13650866200000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>lucas.almeida@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13637903800000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>ana.margarida@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13651170300000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13652338600000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>kaue.medeiros@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13568996500000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>alessiane.carvalho@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13642427700000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13652790000000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13652855400000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13652914700000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13655313900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>gleison.ferreira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13657052200000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>carla.assis@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13657461300000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13657530000000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>luana.marton1@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13651962700000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>jose.junior3@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13656182100000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>renata.matheus@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13149023600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+    <t>Retorno de GO referência-13658628600000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>gisele.mazzucco@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13652554900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>lidiane.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13652755000000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13656348400000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>gisele.cardoso1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13634371200000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>tiago.nascimento@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-10163794000000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-10163804300000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>gisele.cardoso1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13447774300000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13643528500000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>andreia.brixner@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13651645300000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13639611100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13640139300000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13646059600000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13649156100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13650607000000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13653153100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13654596900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13654632600000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13657011100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>erica.cassandre@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13657211900000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>ketlin.vega@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13650187800000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>raphael.callado@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13655111800000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13652433000000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>laudemi.freire@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13652583600000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13655004100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>isabelly.chiarella@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13655182300000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13657459600000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>bernardo.barbosa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13569060800000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>claudia.gomes@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13644017900000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>viviane.lima@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13650891100000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13652223000000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>luciana.belisario@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13651212800000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13642571900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>leandro.gonzaga@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13656398700000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>ana.arruda@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13160697600000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>luciana.mayer@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13651737700000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13502230500000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>patricia.vieira@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13653915100000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>saulo.santiago@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13624067000000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13639510800000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>danilo.ruas@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13645253800000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13652267500000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13653312400000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>eliane.fernandes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13657315600000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>marco.schiabel@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13614187500000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>andreza.libanore@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13645457300000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>fernanda.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13243288900000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>marcia.andreatti@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13478970100000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13648687600000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>fernanda.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13656834500000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>luiza.brandao@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13652489400000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>catia.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13650160300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>viviane.corbari@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13530272400000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13629378400000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13652729100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13653133700000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>daiany.marega1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13653629800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>vitor.mattos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13653079300000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13654500800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>daniele.silva2@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13652522300000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>bruno.ribas@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13650885900000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13653514500000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>kely.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13647859300000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13655246300000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>aline.carpes@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13650115800000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>andreia.cardias@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13651788600000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13651960200000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>fernanda.carneiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13652220800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13652789800000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>olga.terceiro@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13648045400000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13353098700000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>monica.prates@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13639059200000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13653103800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13653208700000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>veruscka.reis@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13653748800000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>raphael.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13649902500000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>adriano.campos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13642328500000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13653485000000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13653765700000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13655614000000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13657024200000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13657206000000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13657986400000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>carolline.acioly@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13650055000000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>claudia.malaggi@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13277727700012 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13617632800000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13656619500000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>cassia.souza@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13644804400000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>raullison.castro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13641244000000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13641530000000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13641557100000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13641593600000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13641625900000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13641662500000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13641676100000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13641953600000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13641958000000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>lucas.monteiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13649895300000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13635059600000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>renato.faillace@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13646734200000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>andrea.duarte@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13652708300000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13652841200000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>flavia.costa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13657871900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>claudia.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13651754700000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>rosana.teixeira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13652733100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>graziela.salvioni@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13216186100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>aline.madeira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13651688400000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>betina.carrasco@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13653357500000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>jonatas.lauretto@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13653465900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13654772800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13655047700000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
   </si>
   <si>
     <t>marcelly.vericimo@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13177784100000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13598387200000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>iury.fuly@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13650432000000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13650666600000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>rodrigo.nascimento@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13558932200000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13650711400000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>jacqueline.mendes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13582298100000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>rafaela.jeronimo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13653282500000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13644035800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13656561000000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13657301600000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13657400700000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13657524100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>cristiane.konrad@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13294378700000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>carla.nascimento@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13385279600000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13412936300000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13513965100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13517944900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13531668900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>larissa.araujo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13341734000000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>ivana.freitas@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13420844300005 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13626131400000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>patricia.soares@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13653668700000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>endyane.marques@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13412054800000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>julianna.printes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13646124300000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13652055700000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13655527800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>jheniffer.emiliano@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13405471600000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13652448100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13652470900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>fabio.ribeiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13653710000000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13654307800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13655875000000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>rosilene.nogueira@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13646463600000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13652984500000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13655828600000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13413903800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>rodrigo.deus@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13652289900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13652660100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13655890800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>andre.benatti@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13645842100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13651766900000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>andrea.farias1@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13644404700000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13653455100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>elaine.sousa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13655536600000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>david.silva2@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13648653200000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13651753600000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>rafael.leite@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13569007400000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>daniella.rodrigues@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13651733700000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13657591700000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>lais.xavier@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13655275300000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13655689500000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>thays.silva@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13653574300000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-88821489400000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>sabrina.azevedo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13649322900000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>ana.salomao@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13657258800000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13652598000000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>leinny.amorim@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13651778500000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13652344900000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>aires.junior@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13654219500000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>enriete.saucedo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13645863100000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>alan.peter@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13646817200000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13657505100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13658679700000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>laila.steil@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13656657600000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>carolina.lima@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13414422800000 Nota 472 - Reentrada OK Produto</t>
+    <t>Retorno de GO referência-13656419100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>marli.rocha@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13635226200000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>ana.rodrigues@allianz.com.br</t>
   </si>
   <si>
-    <t>fabiana.aquino@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13657068100000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13645438600000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>ana.carneiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-61574273000134 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>luisa.almeida@allianz.com.br</t>
+  </si>
+  <si>
+    <t>carlos.neves@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12409236100000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12775353900000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12942732200000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13120703500000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13173664300000 Nota 242 - Retorno Cobrança</t>
   </si>
 </sst>
 </file>
@@ -981,7 +1251,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F98"/>
+  <dimension ref="A1:F173"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.42578125" customWidth="1" collapsed="1"/>
@@ -1057,10 +1327,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>9</v>
@@ -1072,10 +1342,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>9</v>
@@ -1087,7 +1357,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>18</v>
@@ -1102,10 +1372,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>20</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>9</v>
@@ -1117,10 +1387,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>9</v>
@@ -1132,10 +1402,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>9</v>
@@ -1147,10 +1417,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>9</v>
@@ -1162,10 +1432,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>9</v>
@@ -1177,10 +1447,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>9</v>
@@ -1192,10 +1462,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>9</v>
@@ -1207,10 +1477,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>9</v>
@@ -1222,10 +1492,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>9</v>
@@ -1237,10 +1507,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>9</v>
@@ -1252,10 +1522,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>9</v>
@@ -1270,7 +1540,7 @@
         <v>36</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>9</v>
@@ -1282,10 +1552,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>9</v>
@@ -1297,10 +1567,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>9</v>
@@ -1312,10 +1582,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>9</v>
@@ -1327,10 +1597,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s">
         <v>9</v>
@@ -1341,10 +1611,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
         <v>9</v>
@@ -1355,10 +1625,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C25" t="s">
         <v>9</v>
@@ -1369,10 +1639,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C26" t="s">
         <v>9</v>
@@ -1383,10 +1653,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C27" t="s">
         <v>9</v>
@@ -1397,10 +1667,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C28" t="s">
         <v>9</v>
@@ -1411,10 +1681,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C29" t="s">
         <v>9</v>
@@ -1425,10 +1695,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C30" t="s">
         <v>9</v>
@@ -1439,10 +1709,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="C31" t="s">
         <v>9</v>
@@ -1453,10 +1723,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C32" t="s">
         <v>9</v>
@@ -1467,10 +1737,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C33" t="s">
         <v>9</v>
@@ -1481,10 +1751,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C34" t="s">
         <v>9</v>
@@ -1495,10 +1765,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C35" t="s">
         <v>9</v>
@@ -1509,10 +1779,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="C36" t="s">
         <v>9</v>
@@ -1523,10 +1793,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C37" t="s">
         <v>9</v>
@@ -1537,10 +1807,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C38" t="s">
         <v>9</v>
@@ -1551,10 +1821,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C39" t="s">
         <v>9</v>
@@ -1565,10 +1835,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C40" t="s">
         <v>9</v>
@@ -1579,10 +1849,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="C41" t="s">
         <v>9</v>
@@ -1593,10 +1863,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C42" t="s">
         <v>9</v>
@@ -1607,10 +1877,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="C43" t="s">
         <v>9</v>
@@ -1621,10 +1891,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="C44" t="s">
         <v>9</v>
@@ -1635,10 +1905,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="C45" t="s">
         <v>9</v>
@@ -1649,10 +1919,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="C46" t="s">
         <v>9</v>
@@ -1663,10 +1933,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C47" t="s">
         <v>9</v>
@@ -1677,10 +1947,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="C48" t="s">
         <v>9</v>
@@ -1691,10 +1961,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="C49" t="s">
         <v>9</v>
@@ -1705,10 +1975,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C50" t="s">
         <v>9</v>
@@ -1719,10 +1989,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="C51" t="s">
         <v>9</v>
@@ -1733,10 +2003,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="C52" t="s">
         <v>9</v>
@@ -1747,10 +2017,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="C53" t="s">
         <v>9</v>
@@ -1761,10 +2031,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="C54" t="s">
         <v>9</v>
@@ -1775,10 +2045,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="C55" t="s">
         <v>9</v>
@@ -1789,10 +2059,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C56" t="s">
         <v>9</v>
@@ -1803,10 +2073,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="C57" t="s">
         <v>9</v>
@@ -1817,10 +2087,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="C58" t="s">
         <v>9</v>
@@ -1831,10 +2101,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C59" t="s">
         <v>9</v>
@@ -1845,10 +2115,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="C60" t="s">
         <v>9</v>
@@ -1859,10 +2129,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="C61" t="s">
         <v>9</v>
@@ -1873,10 +2143,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="C62" t="s">
         <v>9</v>
@@ -1887,10 +2157,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="C63" t="s">
         <v>9</v>
@@ -1901,10 +2171,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="C64" t="s">
         <v>9</v>
@@ -1915,10 +2185,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C65" t="s">
         <v>9</v>
@@ -1929,10 +2199,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="C66" t="s">
         <v>9</v>
@@ -1943,10 +2213,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="C67" t="s">
         <v>9</v>
@@ -1957,10 +2227,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="C68" t="s">
         <v>9</v>
@@ -1971,10 +2241,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="C69" t="s">
         <v>9</v>
@@ -1985,10 +2255,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="C70" t="s">
         <v>9</v>
@@ -1999,10 +2269,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="C71" t="s">
         <v>9</v>
@@ -2013,10 +2283,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="C72" t="s">
         <v>9</v>
@@ -2027,10 +2297,10 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="C73" t="s">
         <v>9</v>
@@ -2041,10 +2311,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="C74" t="s">
         <v>9</v>
@@ -2055,10 +2325,10 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="C75" t="s">
         <v>9</v>
@@ -2069,10 +2339,10 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="C76" t="s">
         <v>9</v>
@@ -2083,10 +2353,10 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="C77" t="s">
         <v>9</v>
@@ -2097,10 +2367,10 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="C78" t="s">
         <v>9</v>
@@ -2111,10 +2381,10 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="C79" t="s">
         <v>9</v>
@@ -2125,10 +2395,10 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="C80" t="s">
         <v>9</v>
@@ -2139,10 +2409,10 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="C81" t="s">
         <v>9</v>
@@ -2153,10 +2423,10 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="C82" t="s">
         <v>9</v>
@@ -2167,10 +2437,10 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="C83" t="s">
         <v>9</v>
@@ -2181,10 +2451,10 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="C84" t="s">
         <v>9</v>
@@ -2195,10 +2465,10 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="C85" t="s">
         <v>9</v>
@@ -2209,10 +2479,10 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C86" t="s">
         <v>9</v>
@@ -2223,10 +2493,10 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="C87" t="s">
         <v>9</v>
@@ -2237,10 +2507,10 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="C88" t="s">
         <v>9</v>
@@ -2251,10 +2521,10 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="C89" t="s">
         <v>9</v>
@@ -2265,10 +2535,10 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="C90" t="s">
         <v>9</v>
@@ -2279,10 +2549,10 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="C91" t="s">
         <v>9</v>
@@ -2293,10 +2563,10 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C92" t="s">
         <v>9</v>
@@ -2307,10 +2577,10 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="C93" t="s">
         <v>9</v>
@@ -2321,10 +2591,10 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="C94" t="s">
         <v>9</v>
@@ -2335,10 +2605,10 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="C95" t="s">
         <v>9</v>
@@ -2349,10 +2619,10 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="C96" t="s">
         <v>9</v>
@@ -2363,10 +2633,10 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C97" t="s">
         <v>9</v>
@@ -2377,15 +2647,1065 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>156</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C98" t="s">
+        <v>9</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>162</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C99" t="s">
+        <v>9</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>162</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C100" t="s">
+        <v>9</v>
+      </c>
+      <c r="D100" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>156</v>
+      </c>
+      <c r="B101" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="C101" t="s">
+        <v>9</v>
+      </c>
+      <c r="D101" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>158</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C102" t="s">
+        <v>9</v>
+      </c>
+      <c r="D102" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>162</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C103" t="s">
+        <v>9</v>
+      </c>
+      <c r="D103" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>156</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C104" t="s">
+        <v>9</v>
+      </c>
+      <c r="D104" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>169</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C105" t="s">
+        <v>9</v>
+      </c>
+      <c r="D105" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>171</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C106" t="s">
+        <v>9</v>
+      </c>
+      <c r="D106" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>173</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C107" t="s">
+        <v>9</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>169</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C108" t="s">
+        <v>9</v>
+      </c>
+      <c r="D108" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
         <v>176</v>
       </c>
-      <c r="B98" s="6" t="s">
+      <c r="B109" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="C98" t="s">
-        <v>9</v>
-      </c>
-      <c r="D98" s="5" t="s">
+      <c r="C109" t="s">
+        <v>9</v>
+      </c>
+      <c r="D109" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>178</v>
+      </c>
+      <c r="B110" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C110" t="s">
+        <v>9</v>
+      </c>
+      <c r="D110" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>180</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C111" t="s">
+        <v>9</v>
+      </c>
+      <c r="D111" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>182</v>
+      </c>
+      <c r="B112" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C112" t="s">
+        <v>9</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>184</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C113" t="s">
+        <v>9</v>
+      </c>
+      <c r="D113" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>186</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C114" t="s">
+        <v>9</v>
+      </c>
+      <c r="D114" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>188</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C115" t="s">
+        <v>9</v>
+      </c>
+      <c r="D115" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>184</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C116" t="s">
+        <v>9</v>
+      </c>
+      <c r="D116" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>188</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="C117" t="s">
+        <v>9</v>
+      </c>
+      <c r="D117" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>192</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="C118" t="s">
+        <v>9</v>
+      </c>
+      <c r="D118" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>194</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="C119" t="s">
+        <v>9</v>
+      </c>
+      <c r="D119" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>192</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C120" t="s">
+        <v>9</v>
+      </c>
+      <c r="D120" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>192</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C121" t="s">
+        <v>9</v>
+      </c>
+      <c r="D121" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>192</v>
+      </c>
+      <c r="B122" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="C122" t="s">
+        <v>9</v>
+      </c>
+      <c r="D122" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>192</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="C123" t="s">
+        <v>9</v>
+      </c>
+      <c r="D123" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>200</v>
+      </c>
+      <c r="B124" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="C124" t="s">
+        <v>9</v>
+      </c>
+      <c r="D124" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>202</v>
+      </c>
+      <c r="B125" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="C125" t="s">
+        <v>9</v>
+      </c>
+      <c r="D125" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>202</v>
+      </c>
+      <c r="B126" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="C126" t="s">
+        <v>9</v>
+      </c>
+      <c r="D126" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>202</v>
+      </c>
+      <c r="B127" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C127" t="s">
+        <v>9</v>
+      </c>
+      <c r="D127" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>202</v>
+      </c>
+      <c r="B128" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="C128" t="s">
+        <v>9</v>
+      </c>
+      <c r="D128" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>202</v>
+      </c>
+      <c r="B129" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="C129" t="s">
+        <v>9</v>
+      </c>
+      <c r="D129" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>208</v>
+      </c>
+      <c r="B130" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C130" t="s">
+        <v>9</v>
+      </c>
+      <c r="D130" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>210</v>
+      </c>
+      <c r="B131" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="C131" t="s">
+        <v>9</v>
+      </c>
+      <c r="D131" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>208</v>
+      </c>
+      <c r="B132" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="C132" t="s">
+        <v>9</v>
+      </c>
+      <c r="D132" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>213</v>
+      </c>
+      <c r="B133" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="C133" t="s">
+        <v>9</v>
+      </c>
+      <c r="D133" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>213</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C134" t="s">
+        <v>9</v>
+      </c>
+      <c r="D134" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>216</v>
+      </c>
+      <c r="B135" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C135" t="s">
+        <v>9</v>
+      </c>
+      <c r="D135" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>216</v>
+      </c>
+      <c r="B136" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C136" t="s">
+        <v>9</v>
+      </c>
+      <c r="D136" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>216</v>
+      </c>
+      <c r="B137" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="C137" t="s">
+        <v>9</v>
+      </c>
+      <c r="D137" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>220</v>
+      </c>
+      <c r="B138" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C138" t="s">
+        <v>9</v>
+      </c>
+      <c r="D138" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>216</v>
+      </c>
+      <c r="B139" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C139" t="s">
+        <v>9</v>
+      </c>
+      <c r="D139" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>216</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="C140" t="s">
+        <v>9</v>
+      </c>
+      <c r="D140" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>224</v>
+      </c>
+      <c r="B141" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C141" t="s">
+        <v>9</v>
+      </c>
+      <c r="D141" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>226</v>
+      </c>
+      <c r="B142" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="C142" t="s">
+        <v>9</v>
+      </c>
+      <c r="D142" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>224</v>
+      </c>
+      <c r="B143" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="C143" t="s">
+        <v>9</v>
+      </c>
+      <c r="D143" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>224</v>
+      </c>
+      <c r="B144" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="C144" t="s">
+        <v>9</v>
+      </c>
+      <c r="D144" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>230</v>
+      </c>
+      <c r="B145" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C145" t="s">
+        <v>9</v>
+      </c>
+      <c r="D145" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>230</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="C146" t="s">
+        <v>9</v>
+      </c>
+      <c r="D146" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>233</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="C147" t="s">
+        <v>9</v>
+      </c>
+      <c r="D147" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>235</v>
+      </c>
+      <c r="B148" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="C148" t="s">
+        <v>9</v>
+      </c>
+      <c r="D148" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>237</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="C149" t="s">
+        <v>9</v>
+      </c>
+      <c r="D149" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>239</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C150" t="s">
+        <v>9</v>
+      </c>
+      <c r="D150" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>239</v>
+      </c>
+      <c r="B151" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="C151" t="s">
+        <v>9</v>
+      </c>
+      <c r="D151" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>242</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="C152" t="s">
+        <v>9</v>
+      </c>
+      <c r="D152" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>244</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="C153" t="s">
+        <v>9</v>
+      </c>
+      <c r="D153" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>246</v>
+      </c>
+      <c r="B154" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="C154" t="s">
+        <v>9</v>
+      </c>
+      <c r="D154" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>248</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="C155" t="s">
+        <v>9</v>
+      </c>
+      <c r="D155" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>250</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="C156" t="s">
+        <v>9</v>
+      </c>
+      <c r="D156" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>250</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="C157" t="s">
+        <v>9</v>
+      </c>
+      <c r="D157" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>253</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="C158" t="s">
+        <v>9</v>
+      </c>
+      <c r="D158" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>255</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="C159" t="s">
+        <v>9</v>
+      </c>
+      <c r="D159" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>257</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="C160" t="s">
+        <v>9</v>
+      </c>
+      <c r="D160" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>257</v>
+      </c>
+      <c r="B161" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C161" t="s">
+        <v>9</v>
+      </c>
+      <c r="D161" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>257</v>
+      </c>
+      <c r="B162" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C162" t="s">
+        <v>9</v>
+      </c>
+      <c r="D162" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>257</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="C163" t="s">
+        <v>9</v>
+      </c>
+      <c r="D163" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>257</v>
+      </c>
+      <c r="B164" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C164" t="s">
+        <v>9</v>
+      </c>
+      <c r="D164" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>257</v>
+      </c>
+      <c r="B165" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C165" t="s">
+        <v>9</v>
+      </c>
+      <c r="D165" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>257</v>
+      </c>
+      <c r="B166" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="C166" t="s">
+        <v>9</v>
+      </c>
+      <c r="D166" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>259</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="C167" t="s">
+        <v>9</v>
+      </c>
+      <c r="D167" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>261</v>
+      </c>
+      <c r="B168" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="C168" t="s">
+        <v>9</v>
+      </c>
+      <c r="D168" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>262</v>
+      </c>
+      <c r="B169" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C169" t="s">
+        <v>9</v>
+      </c>
+      <c r="D169" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>262</v>
+      </c>
+      <c r="B170" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="C170" t="s">
+        <v>9</v>
+      </c>
+      <c r="D170" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>262</v>
+      </c>
+      <c r="B171" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="C171" t="s">
+        <v>9</v>
+      </c>
+      <c r="D171" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>262</v>
+      </c>
+      <c r="B172" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="C172" t="s">
+        <v>9</v>
+      </c>
+      <c r="D172" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>262</v>
+      </c>
+      <c r="B173" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="C173" t="s">
+        <v>9</v>
+      </c>
+      <c r="D173" s="5" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0749CC63-23FF-4B0A-BE07-C429402A37D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{573C8329-1C82-4F8F-B1FC-9EA132C2CC4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="56">
   <si>
     <t>ERRO</t>
   </si>
@@ -62,274 +62,151 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>lilian.sudati@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13590164800000 Nota 595 - ERRO PDF</t>
+    <t>diogo.junior@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13658815600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
   </si>
   <si>
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>caroline.falcao@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13653133600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>jessica.gimenes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13451812500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>mariana.perez1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13262569900000 Nota 738 - Erro Voucher - exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13476351200000 Nota 738 - Erro Voucher - exclusivo Operações</t>
-  </si>
-  <si>
-    <t>bruna.carneiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13663680600000 Nota 738 - Erro Voucher - exclusivo Operações</t>
-  </si>
-  <si>
-    <t>daniela.carvalho@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13664308400000 Nota 738 - Erro Voucher - exclusivo Operações</t>
-  </si>
-  <si>
-    <t>gessica.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13663863000000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>davi.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13659996600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>ana.ferreira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13665072300000 Nota 738 - Erro Voucher - exclusivo Operações</t>
-  </si>
-  <si>
-    <t>sara.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11440610500000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>ana.margarida@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13401958200000 Nota 738 - Erro Voucher - exclusivo Operações</t>
-  </si>
-  <si>
-    <t>carla.assis@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13664593000000 Nota 738 - Erro Voucher - exclusivo Operações</t>
-  </si>
-  <si>
-    <t>priscila.santana@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13259829300000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>gisele.cardoso1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13660452400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>ketlin.vega@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13664193500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>claudia.gomes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13664099400000 Nota 738 - Erro Voucher - exclusivo Operações</t>
-  </si>
-  <si>
-    <t>mayara.sampaio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13653291700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>andriele.pala@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13576340800000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>luciana.mayer@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13258778100000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>sabrina.meurer@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13663777500000 Nota 738 - Erro Voucher - exclusivo Operações</t>
-  </si>
-  <si>
-    <t>luiza.brandao@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13664793600000 Nota 738 - Erro Voucher - exclusivo Operações</t>
-  </si>
-  <si>
-    <t>monica.betoni@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13664738700000 Nota 738 - Erro Voucher - exclusivo Operações</t>
-  </si>
-  <si>
-    <t>veruscka.reis@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13408986200000 Nota 738 - Erro Voucher - exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13664698000000 Nota 738 - Erro Voucher - exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13665178400000 Nota 738 - Erro Voucher - exclusivo Operações</t>
+    <t>crislaine.trindade@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13658112400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>ana.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13600439500000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>rodrigo.santos1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13664573200000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>luana.marton1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13664481300000 Nota 738 - Erro Voucher - exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13664698900000 Nota 738 - Erro Voucher - exclusivo Operações</t>
+  </si>
+  <si>
+    <t>andreia.brixner@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13663729100000 Nota 738 - Erro Voucher - exclusivo Operações</t>
+  </si>
+  <si>
+    <t>erica.cassandre@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13650782400000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>raphael.callado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13664071500000 Nota 738 - Erro Voucher - exclusivo Operações</t>
+  </si>
+  <si>
+    <t>patricia.vieira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13276561800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>fernanda.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13659399100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>francieli.becker@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13664478100000 Nota 738 - Erro Voucher - exclusivo Operações</t>
+  </si>
+  <si>
+    <t>vitor.mattos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13651677600000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>monica.prates@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13665393800000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13664452400000 Nota 738 - Erro Voucher - exclusivo Operações</t>
+  </si>
+  <si>
+    <t>lucas.godinho@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13669148100000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>claudia.malaggi@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13664388200000 Nota 738 - Erro Voucher - exclusivo Operações</t>
-  </si>
-  <si>
-    <t>daniele.beck@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13172113300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>rafael.xavier@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13624712800016 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13669101800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13669102000000 Nota 595 - ERRO PDF</t>
   </si>
   <si>
     <t>gabriela.logrado@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13661149600000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13663620200000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>betina.carrasco@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13279663600000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>roberta.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13586542500007 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13586542500014 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>matheus.dias@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13664267800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>marcelly.vericimo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13664570500000 Nota 738 - Erro Voucher - exclusivo Operações</t>
-  </si>
-  <si>
-    <t>iury.fuly@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13665158500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>jacqueline.mendes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13663807300000 Nota 738 - Erro Voucher - exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13664334800000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>fabio.ribeiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13664748900000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13272616300000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>francismary.barros@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13569047100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13622472200000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13656418700000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13658032100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>lucas.monteiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13659943200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
   </si>
   <si>
     <t>rosilene.nogueira@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13664093300000 Nota 738 - Erro Voucher - exclusivo Operações</t>
-  </si>
-  <si>
-    <t>diego.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13652024000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>laila.steil@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13515712600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>marli.rocha@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13578529600000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>isabella.barbosa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13647420700000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>carlos.neves@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12712498200000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12842122500000 Nota 242 - Retorno Cobrança</t>
+    <t>Retorno de GO referência-13668486500000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>lais.xavier@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13664319600000 Nota 738 - Erro Voucher - exclusivo Operações</t>
+  </si>
+  <si>
+    <t>ivone.jesus@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13247918900000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>ana.rodrigues@allianz.com.br</t>
   </si>
 </sst>
 </file>
@@ -738,7 +615,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.42578125" customWidth="1" collapsed="1"/>
@@ -829,10 +706,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>9</v>
@@ -844,7 +721,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>18</v>
@@ -1009,10 +886,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>39</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>40</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>9</v>
@@ -1024,10 +901,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>42</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>9</v>
@@ -1039,10 +916,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>43</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>44</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>9</v>
@@ -1054,10 +931,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>9</v>
@@ -1069,10 +946,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>9</v>
@@ -1084,10 +961,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C23" t="s">
         <v>9</v>
@@ -1098,10 +975,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C24" t="s">
         <v>9</v>
@@ -1112,10 +989,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C25" t="s">
         <v>9</v>
@@ -1126,10 +1003,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C26" t="s">
         <v>9</v>
@@ -1143,7 +1020,7 @@
         <v>53</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C27" t="s">
         <v>9</v>
@@ -1154,309 +1031,15 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="C28" t="s">
         <v>9</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>59</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C29" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>61</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C30" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>63</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>65</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C32" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>65</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C33" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>68</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C34" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>70</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C35" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>70</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C36" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>73</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>75</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C38" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>77</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C39" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>79</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C40" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>79</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C41" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>82</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C42" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>84</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C43" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>86</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C44" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>88</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C45" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>90</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C46" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>92</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C47" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>94</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C48" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>94</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C49" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="5" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{573C8329-1C82-4F8F-B1FC-9EA132C2CC4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{462354D7-CD3B-479B-9DC7-F7AED49333EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="42">
   <si>
     <t>ERRO</t>
   </si>
@@ -62,151 +62,109 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>diogo.junior@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13658815600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+    <t>cristiane.barbisan@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13583491800000 Nota 167 - Retorno Cobrança</t>
   </si>
   <si>
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>crislaine.trindade@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13658112400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>ana.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13600439500000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>rodrigo.santos1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13664573200000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>luana.marton1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13664481300000 Nota 738 - Erro Voucher - exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13664698900000 Nota 738 - Erro Voucher - exclusivo Operações</t>
-  </si>
-  <si>
-    <t>andreia.brixner@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13663729100000 Nota 738 - Erro Voucher - exclusivo Operações</t>
-  </si>
-  <si>
-    <t>erica.cassandre@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13650782400000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>raphael.callado@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13664071500000 Nota 738 - Erro Voucher - exclusivo Operações</t>
-  </si>
-  <si>
-    <t>patricia.vieira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13276561800000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>fernanda.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13659399100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>francieli.becker@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13664478100000 Nota 738 - Erro Voucher - exclusivo Operações</t>
-  </si>
-  <si>
-    <t>vitor.mattos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13651677600000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>monica.prates@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13664452400000 Nota 738 - Erro Voucher - exclusivo Operações</t>
-  </si>
-  <si>
-    <t>lucas.godinho@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13669148100000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>claudia.malaggi@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13669101800000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13669102000000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>gabriela.logrado@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13272616300000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>francismary.barros@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13569047100000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13622472200000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13656418700000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13658032100000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>lucas.monteiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13659943200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>rosilene.nogueira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13668486500000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>lais.xavier@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13664319600000 Nota 738 - Erro Voucher - exclusivo Operações</t>
-  </si>
-  <si>
-    <t>ivone.jesus@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13247918900000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>ana.rodrigues@allianz.com.br</t>
+    <t>evaldo.cardoso@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13667082200000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>kaue.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13668474300000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>luiz.inocente@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13658758700000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>enrico.estaliano1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13502013900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13502014000000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>renata.magalhaes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13568957900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>carla.assis@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13665425700000 Nota 738 - Erro Voucher - exclusivo Operações</t>
+  </si>
+  <si>
+    <t>gleison.ferreira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13665474700000 Nota 738 - Erro Voucher - exclusivo Operações</t>
+  </si>
+  <si>
+    <t>renata.matheus@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13665776900000 Nota 738 - Erro Voucher - exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13665895500000 Nota 738 - Erro Voucher - exclusivo Operações</t>
+  </si>
+  <si>
+    <t>tiago.nascimento@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13344917700000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>luiz.santos1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13659192200000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>leandro.machado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13544164300000 Nota 738 - Erro Voucher - exclusivo Operações</t>
+  </si>
+  <si>
+    <t>tullio.yoshinaga@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13623283400000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>shirley.rech@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13454428900000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>olga.terceiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13526943200000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>veruscka.reis@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13665752800000 Nota 738 - Erro Voucher - exclusivo Operações</t>
   </si>
 </sst>
 </file>
@@ -615,7 +573,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.42578125" customWidth="1" collapsed="1"/>
@@ -796,10 +754,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>27</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>28</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>9</v>
@@ -811,10 +769,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>9</v>
@@ -826,10 +784,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>32</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>9</v>
@@ -841,10 +799,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>33</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>34</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>9</v>
@@ -856,10 +814,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>35</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>36</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>9</v>
@@ -871,10 +829,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>9</v>
@@ -886,7 +844,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>39</v>
@@ -913,135 +871,6 @@
         <v>6</v>
       </c>
       <c r="F19" s="3"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" s="6"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" s="3"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>40</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" s="6"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>40</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>47</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>51</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C26" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>53</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>55</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D517296A-5DFC-4AA6-B3FB-C9A36CF2B28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D00FF4-68E0-4683-BA2F-4D0FC5778350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="31">
   <si>
     <t>ERRO</t>
   </si>
@@ -62,58 +62,76 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>simone.lobregate@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13649807200000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+    <t>cristiano.reis@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13669807700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
   </si>
   <si>
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>filipe.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13649860800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>erica.cassandre@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13668341900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>mari.cerutti@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13659216400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>douglas.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13659486300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>renato.faillace@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13674053300000 Nota 595 - ERRO PDF</t>
+    <t>Retorno de GO referência-13673088400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>francieli.becker@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13603626700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>deise.santos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13433802700000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13674993400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
   </si>
   <si>
     <t>thomaz.jesus@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12448112600000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>carlos.neves@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13116443900000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13407159500000 Nota 242 - Retorno Cobrança</t>
+    <t>Retorno de GO referência-12448063500000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12762122900000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13650601900000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>daniella.azevedo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13348600600000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>silvia.plaza@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13494220400000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13518476900000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13518493000000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>mauricio.santo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13578990700000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>tamires.ramiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-10282638900000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-10282650900000 Nota 167 - Retorno Cobrança</t>
   </si>
 </sst>
 </file>
@@ -522,7 +540,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.42578125" customWidth="1" collapsed="1"/>
@@ -569,10 +587,10 @@
     </row>
     <row r="3" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>10</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>11</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>9</v>
@@ -584,10 +602,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>12</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>13</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>9</v>
@@ -598,10 +616,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>14</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>15</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>9</v>
@@ -613,10 +631,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>9</v>
@@ -628,10 +646,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>9</v>
@@ -643,10 +661,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>9</v>
@@ -658,10 +676,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>9</v>
@@ -673,18 +691,108 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" s="6"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B11" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" s="6"/>
+      <c r="C12" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E1FF32C-4565-4DC3-9BC8-C8BD7D3E78EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02753B05-18CB-41E8-B5C1-739818BD3B2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RetornoGo" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="59">
   <si>
     <t>ERRO</t>
   </si>
@@ -62,49 +62,160 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>evaldo.cardoso@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13673554600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+    <t>adriana.coelho@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13681518500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
   </si>
   <si>
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>jessika.pazin@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13682620400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>gleison.ferreira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13438046000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>vanessa.penatti@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13667658900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>olga.terceiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13671770500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>lucas.monteiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13674790000000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+    <t>cristiano.reis@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13371885500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>sara.pereira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13326984400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>raphael.callado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13217354100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>mayara.sampaio@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13683952600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>andriele.pala@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13684447800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>eliane.fernandes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13649129200000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13678005200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>clarissa.cavalli@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13675780100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>flavio.funke@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13679623200000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>leticia.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13683958000000 Nota 595 - ERRO PDF Rertono</t>
+  </si>
+  <si>
+    <t>flavia.costa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13682503600000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>rafael.xavier@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13339715900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>cassia.souza@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13683777400000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>gabriela.logrado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13674288900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13676140800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13676233800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13679562300000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13679678100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13679748800000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13680890900000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13680973900000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13681210600000 Nota 595 - ERRO PDF retorno</t>
   </si>
   <si>
     <t>matheus.dias@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13672717700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+    <t>Retorno de GO referência-13687172400000 Nota 7022 - Help Desk</t>
+  </si>
+  <si>
+    <t>cristiane.konrad@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13659674500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>patricia.vieira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13675732800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>leinny.amorim@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13682322100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>marli.rocha@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13656806500000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>karina.vieira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12628463900000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>tatiana.medina@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13219913000000 Nota 595 - ERRO PDF retorno</t>
   </si>
 </sst>
 </file>
@@ -513,7 +624,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.42578125" customWidth="1" collapsed="1"/>
@@ -646,6 +757,342 @@
         <v>6</v>
       </c>
       <c r="F8" s="6"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" s="6"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" s="6"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" s="3"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" s="6"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" s="3"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" s="6"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F21" s="3"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" s="6"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02753B05-18CB-41E8-B5C1-739818BD3B2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CAD50B0-8B29-45AA-9B58-5E3E390D5D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="149">
   <si>
     <t>ERRO</t>
   </si>
@@ -62,160 +62,430 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>adriana.coelho@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13681518500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+    <t>nathalie.carmo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13676137800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
   </si>
   <si>
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
+    <t>inara.couto@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13680347600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13680833000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>mary.leme@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13671941300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>lilian.sudati@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13672861600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>ana.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13683211500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13685840700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
     <t>cristiano.reis@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13371885500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>sara.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13326984400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>raphael.callado@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13217354100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+    <t>Retorno de GO referência-13682391800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>joao.carvalho2@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13685275800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>valeria.palhares@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13675722300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>matheus.pereira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13656314600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>thais.pessoto@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13684652300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>jefferson.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13549025200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13681924700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>luiz.junior@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13369370100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>daniel.iarrocheski@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13638788600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>caroline.batalha@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13683723400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13684634500000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>bruno.rosa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13552487500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>priscila.brandao@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13668677500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>wilson.filho@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13685918700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>ana.margarida@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13674502800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>lucas.almeida@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13680019700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13680637500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13685848800000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>tatiany.macedo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13396684600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>jose.junior3@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13678789700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13682385300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13683197500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>priscila.santana@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13683174300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>juliana.diniz@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13681344400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>carla.ventura@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13684449000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13685836500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>rafael.petrin@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13360992800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>erica.cassandre@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13545349700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>isabelly.chiarella@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13144298400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>laudemi.freire@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13474653500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13560163600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13685956500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>claudia.gomes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13670105900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
   </si>
   <si>
     <t>mayara.sampaio@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13683952600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>andriele.pala@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13684447800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>eliane.fernandes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13649129200000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13678005200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>clarissa.cavalli@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13675780100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>flavio.funke@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13679623200000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>leticia.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13683958000000 Nota 595 - ERRO PDF Rertono</t>
+    <t>Retorno de GO referência-13685998200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>claudia.assuncao@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13676150100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>fernanda.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13567984100000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>daniele.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13684366300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>leonardo.dache@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13517305100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13530453600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13676969500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13678383100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13679494600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13682287100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>bruna.moi@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13683340300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>jorge.zimke@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13651534600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13678547900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>fabiane.alessi@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13686520600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>adriano.campos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13681725600000 Nota 595 - ERRO PDF retorno</t>
   </si>
   <si>
     <t>flavia.costa@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13682503600000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>rafael.xavier@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13339715900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>cassia.souza@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13683777400000 Nota 595 - ERRO PDF Retorno</t>
+    <t>Retorno de GO referência-13683718200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>gilberto.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11834735800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11834758000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>dyan.leal@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13578013200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>raullison.castro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13684661700000 Nota 595 - ERRO PDF retorno</t>
   </si>
   <si>
     <t>gabriela.logrado@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13674288900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13676140800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13676233800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13679562300000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13679678100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13679748800000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13680890900000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13680973900000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13681210600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>matheus.dias@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13687172400000 Nota 7022 - Help Desk</t>
-  </si>
-  <si>
-    <t>cristiane.konrad@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13659674500000 Nota 595 - ERRO PDF retorno</t>
+    <t>Retorno de GO referência-13681990300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13682822200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>marco.vita@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13685875700000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>lucas.monteiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13676004500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>leandro.susanj@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13680796100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>iury.fuly@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13682221200000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>larissa.araujo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13393853700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13461338200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>patricia.soares@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13684352500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>christian.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13684641300000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>lucas.pereira1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13395202300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>david.silva2@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13308853600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
   </si>
   <si>
     <t>patricia.vieira@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13675732800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>leinny.amorim@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13682322100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>marli.rocha@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13656806500000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>karina.vieira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12628463900000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>tatiana.medina@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13219913000000 Nota 595 - ERRO PDF retorno</t>
+    <t>Retorno de GO referência-13679569400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13682061600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>thays.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13298420100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>alan.peter@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13680010600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>daisy.marangoni@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13682914200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13683005700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>ana.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13675056900000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>adriana.santos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13403859400033 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>carlos.neves@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12497576800000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12602695000000 Nota 242 - Retorno Cobrança</t>
   </si>
 </sst>
 </file>
@@ -624,7 +894,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.42578125" customWidth="1" collapsed="1"/>
@@ -686,10 +956,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>12</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>13</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>9</v>
@@ -700,10 +970,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>14</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>15</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>9</v>
@@ -715,10 +985,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>16</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>9</v>
@@ -730,10 +1000,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>18</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>19</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>9</v>
@@ -745,10 +1015,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>9</v>
@@ -763,7 +1033,7 @@
         <v>20</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>9</v>
@@ -775,10 +1045,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>23</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>9</v>
@@ -790,10 +1060,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>26</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>9</v>
@@ -805,10 +1075,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>27</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>28</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>9</v>
@@ -820,10 +1090,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>9</v>
@@ -835,10 +1105,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>32</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>9</v>
@@ -850,10 +1120,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>9</v>
@@ -865,10 +1135,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>9</v>
@@ -883,7 +1153,7 @@
         <v>35</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>9</v>
@@ -895,7 +1165,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>38</v>
@@ -910,7 +1180,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>39</v>
@@ -925,10 +1195,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>9</v>
@@ -940,10 +1210,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>9</v>
@@ -955,10 +1225,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>9</v>
@@ -970,10 +1240,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C23" t="s">
         <v>9</v>
@@ -984,10 +1254,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C24" t="s">
         <v>9</v>
@@ -998,10 +1268,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C25" t="s">
         <v>9</v>
@@ -1012,10 +1282,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C26" t="s">
         <v>9</v>
@@ -1026,10 +1296,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C27" t="s">
         <v>9</v>
@@ -1040,10 +1310,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C28" t="s">
         <v>9</v>
@@ -1054,10 +1324,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C29" t="s">
         <v>9</v>
@@ -1068,10 +1338,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C30" t="s">
         <v>9</v>
@@ -1082,15 +1352,743 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C31" t="s">
         <v>9</v>
       </c>
       <c r="D31" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C32" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>62</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>65</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>67</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C36" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>69</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>71</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C38" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>69</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C39" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>69</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C40" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>75</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>77</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C42" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>79</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C43" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>81</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C44" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>83</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C45" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>85</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C46" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>85</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C47" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>85</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C48" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>85</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C49" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>85</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C50" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>85</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C51" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>92</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C52" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>94</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>94</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>97</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C55" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>99</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C56" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>101</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C57" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C58" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>103</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C59" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>106</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C60" t="s">
+        <v>9</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>108</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C61" t="s">
+        <v>9</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>110</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C62" t="s">
+        <v>9</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>110</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C63" t="s">
+        <v>9</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>113</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C64" t="s">
+        <v>9</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>115</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C65" t="s">
+        <v>9</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>117</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C66" t="s">
+        <v>9</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>119</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C67" t="s">
+        <v>9</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>121</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C68" t="s">
+        <v>9</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>121</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C69" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>124</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C70" t="s">
+        <v>9</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>126</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C71" t="s">
+        <v>9</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>128</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C72" t="s">
+        <v>9</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>130</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C73" t="s">
+        <v>9</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>132</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C74" t="s">
+        <v>9</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>132</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C75" t="s">
+        <v>9</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>135</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C76" t="s">
+        <v>9</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>137</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C77" t="s">
+        <v>9</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>139</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C78" t="s">
+        <v>9</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>139</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C79" t="s">
+        <v>9</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>142</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C80" t="s">
+        <v>9</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>144</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C81" t="s">
+        <v>9</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>146</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C82" t="s">
+        <v>9</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>146</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C83" t="s">
+        <v>9</v>
+      </c>
+      <c r="D83" s="5" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CAD50B0-8B29-45AA-9B58-5E3E390D5D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ADD1779-E9A7-4FA7-9491-57FA0B0B3809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="138">
   <si>
     <t>ERRO</t>
   </si>
@@ -62,430 +62,397 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>nathalie.carmo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13676137800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+    <t>lilian.sudati@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13684529700000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
   </si>
   <si>
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>inara.couto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13680347600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13680833000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>mary.leme@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13671941300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>lilian.sudati@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13672861600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>ana.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13683211500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13685840700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>cristiano.reis@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13682391800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>joao.carvalho2@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13685275800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>valeria.palhares@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13675722300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>matheus.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13656314600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>thais.pessoto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13684652300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>jefferson.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13549025200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13681924700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>luiz.junior@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13369370100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>daniel.iarrocheski@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13638788600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>caroline.batalha@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13683723400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13684634500000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>bruno.rosa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13552487500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>priscila.brandao@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13668677500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>wilson.filho@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13685918700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>ana.margarida@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13674502800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+    <t>izabela.cuba@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13687352800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>juliano.guimaraes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13682581900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13683296400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>mariana.perez1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13684869900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>daniela.carvalho@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13681907800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>claudia.ribeiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13675615200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13681698300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>davi.pereira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13668938200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>ana.alves1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13681984000000 Nota 595 - ERRO PDF retorno</t>
   </si>
   <si>
     <t>lucas.almeida@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13680019700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13680637500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13685848800000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>tatiany.macedo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13396684600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>jose.junior3@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13678789700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13682385300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13683197500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>priscila.santana@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13683174300000 Nota 595 - ERRO PDF retorno</t>
+    <t>Retorno de GO referência-13680555300000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13682380500000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>bruno.castro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13057206100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>priscila.sousa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13683041400000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13687162500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>sonia.bortoleto@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13683234600000 Nota 595 - ERRO PDF retorno</t>
   </si>
   <si>
     <t>juliana.diniz@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13681344400000 Nota 595 - ERRO PDF retorno</t>
+    <t>Retorno de GO referência-13669524600000 Nota 595 - ERRO PDF retorno</t>
   </si>
   <si>
     <t>carla.ventura@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13684449000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13685836500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>rafael.petrin@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13360992800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+    <t>Retorno de GO referência-13670587000000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13682358300000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>andreia.brixner@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13683837600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13685861300000 Nota 595 - ERRO PDF retorno</t>
   </si>
   <si>
     <t>erica.cassandre@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13545349700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>isabelly.chiarella@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13144298400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>laudemi.freire@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13474653500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13560163600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13685956500000 Nota 595 - ERRO PDF retorno</t>
+    <t>Retorno de GO referência-13679212300000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>leandro.machado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13204431500009 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>bernardo.barbosa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13669839400000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13681521400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>viviane.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13682491300000 Nota 595 - ERRO PDF retorno</t>
   </si>
   <si>
     <t>claudia.gomes@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13670105900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>mayara.sampaio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13685998200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>claudia.assuncao@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13676150100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>fernanda.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13567984100000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>daniele.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13684366300000 Nota 595 - ERRO PDF retorno</t>
+    <t>Retorno de GO referência-13682885000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>luciana.belisario@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13317772000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>andriele.pala@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13672373500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13681814900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13682990200000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>luiza.brandao@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13673501500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>francieli.becker@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13681576300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13682388300000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13685014000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>jaqueline.rissi@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13675863600000 Nota 595 - ERRO PDF retorno</t>
   </si>
   <si>
     <t>leonardo.dache@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13517305100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13530453600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13676969500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13678383100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13679494600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13682287100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>bruna.moi@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13683340300000 Nota 595 - ERRO PDF retorno</t>
+    <t>Retorno de GO referência-13681845200000 Nota 595 - ERRO PDF retorno</t>
   </si>
   <si>
     <t>jorge.zimke@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13651534600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13678547900000 Nota 595 - ERRO PDF retorno</t>
+    <t>Retorno de GO referência-13685793800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>kely.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13682517700000 Nota 595 - ERRO PDF RETORNO</t>
   </si>
   <si>
     <t>fabiane.alessi@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13686520600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>adriano.campos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13681725600000 Nota 595 - ERRO PDF retorno</t>
+    <t>Retorno de GO referência-13684508700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>veruscka.reis@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13684836200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13686956300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>cristiane.silva1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13678194500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13683949000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>marcos.machado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13684892800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>carolline.acioly@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13681235300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
   </si>
   <si>
     <t>flavia.costa@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13683718200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>gilberto.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11834735800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11834758000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>dyan.leal@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13578013200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>raullison.castro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13684661700000 Nota 595 - ERRO PDF retorno</t>
+    <t>Retorno de GO referência-13684890900000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>rodrigo.amorim@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13318807800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13678723400000 Nota 595 - ERRO PDF Retorno</t>
   </si>
   <si>
     <t>gabriela.logrado@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13681990300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13682822200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>marco.vita@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13685875700000 Nota 595 - ERRO PDF RETORNO</t>
+    <t>Retorno de GO referência-13278115300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13689011700000 Nota 595 - ERRO PDF retorno</t>
   </si>
   <si>
     <t>lucas.monteiro@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13676004500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>leandro.susanj@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13680796100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+    <t>Retorno de GO referência-13680094600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13680128800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>aline.madeira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13682169200000 Nota 595 - ERRO PDF RETORNO</t>
   </si>
   <si>
     <t>iury.fuly@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13682221200000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+    <t>Retorno de GO referência-13370447500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13370508800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13531205200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13634415300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>marcelly.vericimo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13685512500000 Nota 595 - ERRO PDF retorno</t>
   </si>
   <si>
     <t>larissa.araujo@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13393853700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13461338200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>patricia.soares@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13684352500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>christian.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13684641300000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>lucas.pereira1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13395202300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>david.silva2@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13308853600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>patricia.vieira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13679569400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13682061600000 Nota 595 - ERRO PDF retorno</t>
+    <t>Retorno de GO referência-13686676300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>fabio.ribeiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13681728800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>aparecida.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13673421800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>andrea.farias1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13680690300000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13681458800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13682538300000 Nota 595 - ERRO PDF Retorno</t>
   </si>
   <si>
     <t>thays.silva@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13298420100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>alan.peter@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13680010600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>daisy.marangoni@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13682914200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13683005700000 Nota 595 - ERRO PDF retorno</t>
+    <t>Retorno de GO referência-13681527000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>sabrina.azevedo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13656782600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>leinny.amorim@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13679157000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>rosilene.nogueira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13686613900000 Nota 595 - ERRO PDF retorno</t>
   </si>
   <si>
     <t>ana.rodrigues@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13675056900000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>adriana.santos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13403859400033 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>carlos.neves@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12497576800000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12602695000000 Nota 242 - Retorno Cobrança</t>
+    <t>Retorno de GO referência-13675484200000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>karina.vieira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12628463900000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>mauricio.santo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13371129100000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>ana.carneiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-15517074000177 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>renata.souza1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13667912100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>rogerio.souza@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13514359300000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13588429900000 Nota 167 - Retorno Cobrança</t>
   </si>
 </sst>
 </file>
@@ -894,7 +861,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.42578125" customWidth="1" collapsed="1"/>
@@ -956,10 +923,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>9</v>
@@ -970,7 +937,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>14</v>
@@ -1015,10 +982,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>9</v>
@@ -1030,7 +997,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>21</v>
@@ -1090,10 +1057,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>29</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>9</v>
@@ -1105,10 +1072,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>9</v>
@@ -1120,7 +1087,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>32</v>
@@ -1135,10 +1102,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>33</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>34</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>9</v>
@@ -1150,10 +1117,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>35</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>36</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>9</v>
@@ -1165,10 +1132,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>9</v>
@@ -1180,7 +1147,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>39</v>
@@ -1195,10 +1162,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>41</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>9</v>
@@ -1210,10 +1177,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>42</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>43</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>9</v>
@@ -1225,10 +1192,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>9</v>
@@ -1240,10 +1207,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
         <v>9</v>
@@ -1254,10 +1221,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C24" t="s">
         <v>9</v>
@@ -1268,10 +1235,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C25" t="s">
         <v>9</v>
@@ -1285,7 +1252,7 @@
         <v>46</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C26" t="s">
         <v>9</v>
@@ -1296,10 +1263,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>52</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>53</v>
       </c>
       <c r="C27" t="s">
         <v>9</v>
@@ -1310,10 +1277,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="C28" t="s">
         <v>9</v>
@@ -1324,7 +1291,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>56</v>
@@ -1338,10 +1305,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C30" t="s">
         <v>9</v>
@@ -1352,7 +1319,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>59</v>
@@ -1366,10 +1333,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>57</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>60</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>61</v>
       </c>
       <c r="C32" t="s">
         <v>9</v>
@@ -1380,10 +1347,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>61</v>
+      </c>
+      <c r="B33" s="6" t="s">
         <v>62</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>63</v>
       </c>
       <c r="C33" t="s">
         <v>9</v>
@@ -1394,7 +1361,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>64</v>
@@ -1408,10 +1375,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>63</v>
+      </c>
+      <c r="B35" s="6" t="s">
         <v>65</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>66</v>
       </c>
       <c r="C35" t="s">
         <v>9</v>
@@ -1422,10 +1389,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C36" t="s">
         <v>9</v>
@@ -1436,10 +1403,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C37" t="s">
         <v>9</v>
@@ -1450,10 +1417,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C38" t="s">
         <v>9</v>
@@ -1464,10 +1431,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C39" t="s">
         <v>9</v>
@@ -1478,7 +1445,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>74</v>
@@ -1520,10 +1487,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>77</v>
+      </c>
+      <c r="B43" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="C43" t="s">
         <v>9</v>
@@ -1534,10 +1501,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>80</v>
+      </c>
+      <c r="B44" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>82</v>
       </c>
       <c r="C44" t="s">
         <v>9</v>
@@ -1548,10 +1515,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C45" t="s">
         <v>9</v>
@@ -1562,10 +1529,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C46" t="s">
         <v>9</v>
@@ -1579,7 +1546,7 @@
         <v>85</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C47" t="s">
         <v>9</v>
@@ -1590,7 +1557,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>88</v>
@@ -1604,10 +1571,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C49" t="s">
         <v>9</v>
@@ -1618,10 +1585,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C50" t="s">
         <v>9</v>
@@ -1632,10 +1599,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C51" t="s">
         <v>9</v>
@@ -1649,7 +1616,7 @@
         <v>92</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C52" t="s">
         <v>9</v>
@@ -1660,10 +1627,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C53" t="s">
         <v>9</v>
@@ -1674,10 +1641,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C54" t="s">
         <v>9</v>
@@ -1688,10 +1655,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C55" t="s">
         <v>9</v>
@@ -1702,10 +1669,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C56" t="s">
         <v>9</v>
@@ -1716,7 +1683,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>102</v>
@@ -1730,10 +1697,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>100</v>
+      </c>
+      <c r="B58" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="C58" t="s">
         <v>9</v>
@@ -1744,10 +1711,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C59" t="s">
         <v>9</v>
@@ -1758,10 +1725,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>105</v>
+      </c>
+      <c r="B60" s="6" t="s">
         <v>106</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="C60" t="s">
         <v>9</v>
@@ -1772,10 +1739,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>107</v>
+      </c>
+      <c r="B61" s="6" t="s">
         <v>108</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>109</v>
       </c>
       <c r="C61" t="s">
         <v>9</v>
@@ -1786,10 +1753,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>109</v>
+      </c>
+      <c r="B62" s="6" t="s">
         <v>110</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>111</v>
       </c>
       <c r="C62" t="s">
         <v>9</v>
@@ -1800,7 +1767,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>112</v>
@@ -1828,10 +1795,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>113</v>
+      </c>
+      <c r="B65" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>116</v>
       </c>
       <c r="C65" t="s">
         <v>9</v>
@@ -1842,10 +1809,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C66" t="s">
         <v>9</v>
@@ -1856,10 +1823,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C67" t="s">
         <v>9</v>
@@ -1870,10 +1837,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C68" t="s">
         <v>9</v>
@@ -1887,7 +1854,7 @@
         <v>121</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C69" t="s">
         <v>9</v>
@@ -1898,10 +1865,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>123</v>
+      </c>
+      <c r="B70" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="C70" t="s">
         <v>9</v>
@@ -1912,10 +1879,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>125</v>
+      </c>
+      <c r="B71" s="6" t="s">
         <v>126</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>127</v>
       </c>
       <c r="C71" t="s">
         <v>9</v>
@@ -1926,10 +1893,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>127</v>
+      </c>
+      <c r="B72" s="6" t="s">
         <v>128</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>129</v>
       </c>
       <c r="C72" t="s">
         <v>9</v>
@@ -1940,10 +1907,10 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>129</v>
+      </c>
+      <c r="B73" s="6" t="s">
         <v>130</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>131</v>
       </c>
       <c r="C73" t="s">
         <v>9</v>
@@ -1954,10 +1921,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>131</v>
+      </c>
+      <c r="B74" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="C74" t="s">
         <v>9</v>
@@ -1968,7 +1935,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>134</v>
@@ -1996,99 +1963,15 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>135</v>
+      </c>
+      <c r="B77" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="B77" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="C77" t="s">
         <v>9</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>139</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="C78" t="s">
-        <v>9</v>
-      </c>
-      <c r="D78" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>139</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="C79" t="s">
-        <v>9</v>
-      </c>
-      <c r="D79" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>142</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="C80" t="s">
-        <v>9</v>
-      </c>
-      <c r="D80" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>144</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="C81" t="s">
-        <v>9</v>
-      </c>
-      <c r="D81" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>146</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C82" t="s">
-        <v>9</v>
-      </c>
-      <c r="D82" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>146</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="C83" t="s">
-        <v>9</v>
-      </c>
-      <c r="D83" s="5" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/EnvioRetornoGo.xlsx
+++ b/Treinamento/EnvioRetornoGo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ADD1779-E9A7-4FA7-9491-57FA0B0B3809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C926C52-3361-474E-81C9-BFD46666BFC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="107">
   <si>
     <t>ERRO</t>
   </si>
@@ -62,397 +62,304 @@
     <t>Processar</t>
   </si>
   <si>
+    <t>nathalie.carmo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13319787800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
+  </si>
+  <si>
+    <t>inara.couto@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13692331300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
     <t>lilian.sudati@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13684529700000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
-  </si>
-  <si>
-    <t>izabela.cuba@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13687352800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>juliano.guimaraes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13682581900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13683296400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>mariana.perez1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13684869900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>daniela.carvalho@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13681907800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>claudia.ribeiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13675615200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13681698300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>davi.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13668938200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>ana.alves1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13681984000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>lucas.almeida@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13680555300000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13682380500000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>bruno.castro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13057206100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>priscila.sousa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13683041400000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13687162500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>sonia.bortoleto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13683234600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>juliana.diniz@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13669524600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>carla.ventura@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13670587000000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13682358300000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>andreia.brixner@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13683837600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13685861300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>erica.cassandre@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13679212300000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>leandro.machado@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13204431500009 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>bernardo.barbosa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13669839400000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13681521400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>viviane.lima@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13682491300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>claudia.gomes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13682885000000 Nota 595 - ERRO PDF retorno</t>
+    <t>Retorno de GO referência-13689802900000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>evaldo.cardoso@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13679419100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>joao.carvalho2@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13679384700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>valeria.palhares@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13687171200000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>matheus.pereira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13685091200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>ana.ferreira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13329202400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>bruno.rosa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13684783000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13684935900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>daniela.gui@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-33168116807 Nota 531 - Alteração ou correção dados cadastrais</t>
+  </si>
+  <si>
+    <t>gisele.cardoso1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-6610098905 Nota 531 - Alteração ou correção dados cadastrais</t>
+  </si>
+  <si>
+    <t>caroline.wojciechowski@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13683786500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-30741709000109 Nota 531 - Alteração ou correção dados cadastrais</t>
+  </si>
+  <si>
+    <t>rafael.petrin@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13687235700000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13687238500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13687248100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13687249100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13689704100000 Nota 595 - ERRO PDF retorno</t>
   </si>
   <si>
     <t>luciana.belisario@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13317772000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+    <t>Retorno de GO referência-13281844300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
   </si>
   <si>
     <t>andriele.pala@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13672373500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13681814900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13682990200000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>luiza.brandao@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13673501500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>francieli.becker@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13681576300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13682388300000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13685014000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>jaqueline.rissi@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13675863600000 Nota 595 - ERRO PDF retorno</t>
+    <t>Retorno de GO referência-13684719500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>ana.arruda@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13690307000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>fernanda.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13552257600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>daniele.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13684760100000 Nota 595 - ERRO PDF retorno</t>
   </si>
   <si>
     <t>leonardo.dache@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13681845200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>jorge.zimke@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13685793800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>kely.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13682517700000 Nota 595 - ERRO PDF RETORNO</t>
+    <t>Retorno de GO referência-13681452200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>bruno.ribas@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13687067800000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>andreia.cardias@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13684285600000 Nota 595 - ERRO PDF retorno</t>
   </si>
   <si>
     <t>fabiane.alessi@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13684508700000 Nota 595 - ERRO PDF retorno</t>
+    <t>Retorno de GO referência-36761664772 Nota 531 - Alteração ou correção dados cadastrais</t>
   </si>
   <si>
     <t>veruscka.reis@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13684836200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13686956300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>cristiane.silva1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13678194500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13683949000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>marcos.machado@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13684892800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>carolline.acioly@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13681235300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+    <t>Retorno de GO referência-13256938300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>leticia.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13636830200000 Nota 595 - ERRO PDF retorno</t>
   </si>
   <si>
     <t>flavia.costa@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13684890900000 Nota 595 - ERRO PDF Retorno</t>
+    <t>Retorno de GO referência-13689805300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>eduardo.marques@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13681746800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
   </si>
   <si>
     <t>rodrigo.amorim@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13318807800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13678723400000 Nota 595 - ERRO PDF Retorno</t>
+    <t>Retorno de GO referência-13688698200000 Nota 595 - ERRO PDF retorno</t>
   </si>
   <si>
     <t>gabriela.logrado@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13278115300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13689011700000 Nota 595 - ERRO PDF retorno</t>
+    <t>Retorno de GO referência-13687143800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13688032400000 Nota 595 - ERRO PDF retorno</t>
   </si>
   <si>
     <t>lucas.monteiro@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13680094600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13680128800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>aline.madeira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13682169200000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>iury.fuly@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13370447500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13370508800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13531205200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13634415300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>marcelly.vericimo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13685512500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>larissa.araujo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13686676300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>fabio.ribeiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13681728800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>aparecida.rodrigues@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13673421800000 Nota 595 - ERRO PDF retorno</t>
+    <t>Retorno de GO referência-13679933200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>mario.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13688829000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>rodrigo.nascimento@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13681504900000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>patricia.soares@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13683722400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13684920500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>sofia.magalhaes1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13687722400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13689731400000 Nota 595 - ERRO PDF Retorno</t>
   </si>
   <si>
     <t>andrea.farias1@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13680690300000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13681458800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13682538300000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>thays.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13681527000000 Nota 595 - ERRO PDF retorno</t>
+    <t>Retorno de GO referência-13678868000000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>rafael.leite@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13166022600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>diego.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13465035000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
   </si>
   <si>
     <t>sabrina.azevedo@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13656782600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>leinny.amorim@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13679157000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>rosilene.nogueira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13686613900000 Nota 595 - ERRO PDF retorno</t>
+    <t>Retorno de GO referência-13692934000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>daisy.marangoni@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13685865700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>laila.steil@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13688151100000 Nota 595 - ERRO PDF Retorno</t>
   </si>
   <si>
     <t>ana.rodrigues@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13675484200000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>karina.vieira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12628463900000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>mauricio.santo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13371129100000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>ana.carneiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-15517074000177 Nota 242 - Retorno Cobrança</t>
+    <t>Retorno de GO referência-13216882400000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>marli.rocha@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13674772000000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>marcia.pereira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13327744200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>jeisis.arruda@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13671262500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>caroline.martins@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13681305600000 Nota 595 - ERRO PDF retorno</t>
   </si>
   <si>
     <t>renata.souza1@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13667912100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>rogerio.souza@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13514359300000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13588429900000 Nota 167 - Retorno Cobrança</t>
+    <t>Retorno de GO referência-13682885100000 Nota 595 - ERRO PDF retorno</t>
   </si>
 </sst>
 </file>
@@ -861,7 +768,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.42578125" customWidth="1" collapsed="1"/>
@@ -937,10 +844,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>9</v>
@@ -952,10 +859,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>9</v>
@@ -967,10 +874,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>9</v>
@@ -982,10 +889,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>9</v>
@@ -997,10 +904,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>9</v>
@@ -1012,10 +919,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>9</v>
@@ -1030,7 +937,7 @@
         <v>24</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>9</v>
@@ -1042,10 +949,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>9</v>
@@ -1057,10 +964,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>9</v>
@@ -1072,10 +979,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>9</v>
@@ -1087,10 +994,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>9</v>
@@ -1102,10 +1009,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>9</v>
@@ -1120,7 +1027,7 @@
         <v>34</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>9</v>
@@ -1132,7 +1039,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>37</v>
@@ -1147,10 +1054,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>38</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>39</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>9</v>
@@ -1162,10 +1069,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>9</v>
@@ -1177,10 +1084,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>42</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>9</v>
@@ -1192,7 +1099,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>43</v>
@@ -1249,10 +1156,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C26" t="s">
         <v>9</v>
@@ -1263,10 +1170,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C27" t="s">
         <v>9</v>
@@ -1277,10 +1184,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C28" t="s">
         <v>9</v>
@@ -1291,10 +1198,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C29" t="s">
         <v>9</v>
@@ -1305,10 +1212,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C30" t="s">
         <v>9</v>
@@ -1319,10 +1226,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C31" t="s">
         <v>9</v>
@@ -1333,10 +1240,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C32" t="s">
         <v>9</v>
@@ -1347,10 +1254,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C33" t="s">
         <v>9</v>
@@ -1361,10 +1268,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C34" t="s">
         <v>9</v>
@@ -1375,10 +1282,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C35" t="s">
         <v>9</v>
@@ -1389,10 +1296,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C36" t="s">
         <v>9</v>
@@ -1403,10 +1310,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C37" t="s">
         <v>9</v>
@@ -1417,10 +1324,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C38" t="s">
         <v>9</v>
@@ -1431,10 +1338,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C39" t="s">
         <v>9</v>
@@ -1445,10 +1352,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C40" t="s">
         <v>9</v>
@@ -1459,10 +1366,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C41" t="s">
         <v>9</v>
@@ -1473,10 +1380,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C42" t="s">
         <v>9</v>
@@ -1487,10 +1394,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C43" t="s">
         <v>9</v>
@@ -1501,10 +1408,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C44" t="s">
         <v>9</v>
@@ -1515,10 +1422,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C45" t="s">
         <v>9</v>
@@ -1529,10 +1436,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C46" t="s">
         <v>9</v>
@@ -1543,10 +1450,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C47" t="s">
         <v>9</v>
@@ -1557,10 +1464,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C48" t="s">
         <v>9</v>
@@ -1571,10 +1478,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C49" t="s">
         <v>9</v>
@@ -1585,10 +1492,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C50" t="s">
         <v>9</v>
@@ -1599,10 +1506,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C51" t="s">
         <v>9</v>
@@ -1613,10 +1520,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C52" t="s">
         <v>9</v>
@@ -1627,10 +1534,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C53" t="s">
         <v>9</v>
@@ -1641,10 +1548,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C54" t="s">
         <v>9</v>
@@ -1655,323 +1562,15 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C55" t="s">
         <v>9</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>100</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C56" t="s">
-        <v>9</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>100</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C57" t="s">
-        <v>9</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>100</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C58" t="s">
-        <v>9</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>100</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C59" t="s">
-        <v>9</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>105</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C60" t="s">
-        <v>9</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>107</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C61" t="s">
-        <v>9</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>109</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C62" t="s">
-        <v>9</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>111</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C63" t="s">
-        <v>9</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>113</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="C64" t="s">
-        <v>9</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>113</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C65" t="s">
-        <v>9</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>113</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="C66" t="s">
-        <v>9</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>117</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C67" t="s">
-        <v>9</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>119</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="C68" t="s">
-        <v>9</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>121</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="C69" t="s">
-        <v>9</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>123</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="C70" t="s">
-        <v>9</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>125</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="C71" t="s">
-        <v>9</v>
-      </c>
-      <c r="D71" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>127</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C72" t="s">
-        <v>9</v>
-      </c>
-      <c r="D72" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>129</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="C73" t="s">
-        <v>9</v>
-      </c>
-      <c r="D73" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>131</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="C74" t="s">
-        <v>9</v>
-      </c>
-      <c r="D74" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>133</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="C75" t="s">
-        <v>9</v>
-      </c>
-      <c r="D75" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>135</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="C76" t="s">
-        <v>9</v>
-      </c>
-      <c r="D76" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>135</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="C77" t="s">
-        <v>9</v>
-      </c>
-      <c r="D77" s="5" t="s">
         <v>6</v>
       </c>
     </row>
